--- a/review-results/河北实时运行及市场出清数据-20261016.xlsx
+++ b/review-results/河北实时运行及市场出清数据-20261016.xlsx
@@ -4289,12 +4289,8 @@
       <ns0:c r="C2" s="1" t="n">
         <ns0:v>1</ns0:v>
       </ns0:c>
-      <ns0:c r="D2" s="1" t="n">
-        <ns0:v>355.48</ns0:v>
-      </ns0:c>
-      <ns0:c r="E2" s="1" t="n">
-        <ns0:v>433.51</ns0:v>
-      </ns0:c>
+      <ns0:c r="D2" s="1"/>
+      <ns0:c r="E2" s="1"/>
       <ns0:c r="F2" s="1" t="n">
         <ns0:v>33</ns0:v>
       </ns0:c>
@@ -4328,9 +4324,7 @@
       <ns0:c r="P2" s="1" t="n">
         <ns0:v>62</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q2" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q2"/>
     </ns0:row>
     <ns0:row r="3" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A3" s="6" t="n">
@@ -4342,12 +4336,8 @@
       <ns0:c r="C3" s="1" t="n">
         <ns0:v>1</ns0:v>
       </ns0:c>
-      <ns0:c r="D3" s="1" t="n">
-        <ns0:v>355.48</ns0:v>
-      </ns0:c>
-      <ns0:c r="E3" s="1" t="n">
-        <ns0:v>474.79</ns0:v>
-      </ns0:c>
+      <ns0:c r="D3" s="1"/>
+      <ns0:c r="E3" s="1"/>
       <ns0:c r="F3" s="1" t="n">
         <ns0:v>33</ns0:v>
       </ns0:c>
@@ -4381,9 +4371,7 @@
       <ns0:c r="P3" s="1" t="n">
         <ns0:v>62</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q3" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q3"/>
     </ns0:row>
     <ns0:row r="4" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A4" s="6" t="n">
@@ -4395,12 +4383,8 @@
       <ns0:c r="C4" s="1" t="n">
         <ns0:v>1</ns0:v>
       </ns0:c>
-      <ns0:c r="D4" s="1" t="n">
-        <ns0:v>355.48</ns0:v>
-      </ns0:c>
-      <ns0:c r="E4" s="1" t="n">
-        <ns0:v>465</ns0:v>
-      </ns0:c>
+      <ns0:c r="D4" s="1"/>
+      <ns0:c r="E4" s="1"/>
       <ns0:c r="F4" s="1" t="n">
         <ns0:v>33</ns0:v>
       </ns0:c>
@@ -4434,9 +4418,7 @@
       <ns0:c r="P4" s="1" t="n">
         <ns0:v>63</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q4" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q4"/>
     </ns0:row>
     <ns0:row r="5" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A5" s="6" t="n">
@@ -4448,12 +4430,8 @@
       <ns0:c r="C5" s="1" t="n">
         <ns0:v>1</ns0:v>
       </ns0:c>
-      <ns0:c r="D5" s="1" t="n">
-        <ns0:v>355.48</ns0:v>
-      </ns0:c>
-      <ns0:c r="E5" s="1" t="n">
-        <ns0:v>464.8</ns0:v>
-      </ns0:c>
+      <ns0:c r="D5" s="1"/>
+      <ns0:c r="E5" s="1"/>
       <ns0:c r="F5" s="1" t="n">
         <ns0:v>33</ns0:v>
       </ns0:c>
@@ -4487,9 +4465,7 @@
       <ns0:c r="P5" s="1" t="n">
         <ns0:v>63</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q5" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q5"/>
     </ns0:row>
     <ns0:row r="6" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A6" s="6" t="n">
@@ -4501,12 +4477,8 @@
       <ns0:c r="C6" s="1" t="n">
         <ns0:v>2</ns0:v>
       </ns0:c>
-      <ns0:c r="D6" s="1" t="n">
-        <ns0:v>369.51</ns0:v>
-      </ns0:c>
-      <ns0:c r="E6" s="1" t="n">
-        <ns0:v>445</ns0:v>
-      </ns0:c>
+      <ns0:c r="D6" s="1"/>
+      <ns0:c r="E6" s="1"/>
       <ns0:c r="F6" s="1" t="n">
         <ns0:v>33</ns0:v>
       </ns0:c>
@@ -4540,9 +4512,7 @@
       <ns0:c r="P6" s="1" t="n">
         <ns0:v>63</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q6" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q6"/>
     </ns0:row>
     <ns0:row r="7" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A7" s="6" t="n">
@@ -4554,12 +4524,8 @@
       <ns0:c r="C7" s="1" t="n">
         <ns0:v>2</ns0:v>
       </ns0:c>
-      <ns0:c r="D7" s="1" t="n">
-        <ns0:v>369.51</ns0:v>
-      </ns0:c>
-      <ns0:c r="E7" s="1" t="n">
-        <ns0:v>441.51</ns0:v>
-      </ns0:c>
+      <ns0:c r="D7" s="1"/>
+      <ns0:c r="E7" s="1"/>
       <ns0:c r="F7" s="1" t="n">
         <ns0:v>33</ns0:v>
       </ns0:c>
@@ -4593,9 +4559,7 @@
       <ns0:c r="P7" s="1" t="n">
         <ns0:v>63</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q7" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q7"/>
     </ns0:row>
     <ns0:row r="8" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A8" s="6" t="n">
@@ -4607,12 +4571,8 @@
       <ns0:c r="C8" s="1" t="n">
         <ns0:v>2</ns0:v>
       </ns0:c>
-      <ns0:c r="D8" s="1" t="n">
-        <ns0:v>369.51</ns0:v>
-      </ns0:c>
-      <ns0:c r="E8" s="1" t="n">
-        <ns0:v>430.36</ns0:v>
-      </ns0:c>
+      <ns0:c r="D8" s="1"/>
+      <ns0:c r="E8" s="1"/>
       <ns0:c r="F8" s="1" t="n">
         <ns0:v>33</ns0:v>
       </ns0:c>
@@ -4646,9 +4606,7 @@
       <ns0:c r="P8" s="1" t="n">
         <ns0:v>64</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q8" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q8"/>
     </ns0:row>
     <ns0:row r="9" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A9" s="6" t="n">
@@ -4660,12 +4618,8 @@
       <ns0:c r="C9" s="1" t="n">
         <ns0:v>2</ns0:v>
       </ns0:c>
-      <ns0:c r="D9" s="1" t="n">
-        <ns0:v>369.35</ns0:v>
-      </ns0:c>
-      <ns0:c r="E9" s="1" t="n">
-        <ns0:v>431.57</ns0:v>
-      </ns0:c>
+      <ns0:c r="D9" s="1"/>
+      <ns0:c r="E9" s="1"/>
       <ns0:c r="F9" s="1" t="n">
         <ns0:v>33</ns0:v>
       </ns0:c>
@@ -4699,9 +4653,7 @@
       <ns0:c r="P9" s="1" t="n">
         <ns0:v>64</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q9" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q9"/>
     </ns0:row>
     <ns0:row r="10" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A10" s="6" t="n">
@@ -4713,12 +4665,8 @@
       <ns0:c r="C10" s="1" t="n">
         <ns0:v>3</ns0:v>
       </ns0:c>
-      <ns0:c r="D10" s="1" t="n">
-        <ns0:v>390.54</ns0:v>
-      </ns0:c>
-      <ns0:c r="E10" s="1" t="n">
-        <ns0:v>474.23</ns0:v>
-      </ns0:c>
+      <ns0:c r="D10" s="1"/>
+      <ns0:c r="E10" s="1"/>
       <ns0:c r="F10" s="1" t="n">
         <ns0:v>133</ns0:v>
       </ns0:c>
@@ -4752,9 +4700,7 @@
       <ns0:c r="P10" s="1" t="n">
         <ns0:v>64</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q10" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q10"/>
     </ns0:row>
     <ns0:row r="11" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A11" s="6" t="n">
@@ -4766,12 +4712,8 @@
       <ns0:c r="C11" s="1" t="n">
         <ns0:v>3</ns0:v>
       </ns0:c>
-      <ns0:c r="D11" s="1" t="n">
-        <ns0:v>390.54</ns0:v>
-      </ns0:c>
-      <ns0:c r="E11" s="1" t="n">
-        <ns0:v>465</ns0:v>
-      </ns0:c>
+      <ns0:c r="D11" s="1"/>
+      <ns0:c r="E11" s="1"/>
       <ns0:c r="F11" s="1" t="n">
         <ns0:v>133</ns0:v>
       </ns0:c>
@@ -4805,9 +4747,7 @@
       <ns0:c r="P11" s="1" t="n">
         <ns0:v>64</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q11" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q11"/>
     </ns0:row>
     <ns0:row r="12" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A12" s="6" t="n">
@@ -4819,12 +4759,8 @@
       <ns0:c r="C12" s="1" t="n">
         <ns0:v>3</ns0:v>
       </ns0:c>
-      <ns0:c r="D12" s="1" t="n">
-        <ns0:v>390.54</ns0:v>
-      </ns0:c>
-      <ns0:c r="E12" s="1" t="n">
-        <ns0:v>433.73</ns0:v>
-      </ns0:c>
+      <ns0:c r="D12" s="1"/>
+      <ns0:c r="E12" s="1"/>
       <ns0:c r="F12" s="1" t="n">
         <ns0:v>133</ns0:v>
       </ns0:c>
@@ -4858,9 +4794,7 @@
       <ns0:c r="P12" s="1" t="n">
         <ns0:v>64</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q12" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q12"/>
     </ns0:row>
     <ns0:row r="13" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A13" s="6" t="n">
@@ -4872,12 +4806,8 @@
       <ns0:c r="C13" s="1" t="n">
         <ns0:v>3</ns0:v>
       </ns0:c>
-      <ns0:c r="D13" s="1" t="n">
-        <ns0:v>390.54</ns0:v>
-      </ns0:c>
-      <ns0:c r="E13" s="1" t="n">
-        <ns0:v>429.32</ns0:v>
-      </ns0:c>
+      <ns0:c r="D13" s="1"/>
+      <ns0:c r="E13" s="1"/>
       <ns0:c r="F13" s="1" t="n">
         <ns0:v>0</ns0:v>
       </ns0:c>
@@ -4911,9 +4841,7 @@
       <ns0:c r="P13" s="1" t="n">
         <ns0:v>64</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q13" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q13"/>
     </ns0:row>
     <ns0:row r="14" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A14" s="6" t="n">
@@ -4925,12 +4853,8 @@
       <ns0:c r="C14" s="1" t="n">
         <ns0:v>4</ns0:v>
       </ns0:c>
-      <ns0:c r="D14" s="1" t="n">
-        <ns0:v>420</ns0:v>
-      </ns0:c>
-      <ns0:c r="E14" s="1" t="n">
-        <ns0:v>415.25</ns0:v>
-      </ns0:c>
+      <ns0:c r="D14" s="1"/>
+      <ns0:c r="E14" s="1"/>
       <ns0:c r="F14" s="1" t="n">
         <ns0:v>0</ns0:v>
       </ns0:c>
@@ -4964,9 +4888,7 @@
       <ns0:c r="P14" s="1" t="n">
         <ns0:v>64</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q14" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q14"/>
     </ns0:row>
     <ns0:row r="15" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A15" s="6" t="n">
@@ -4978,12 +4900,8 @@
       <ns0:c r="C15" s="1" t="n">
         <ns0:v>4</ns0:v>
       </ns0:c>
-      <ns0:c r="D15" s="1" t="n">
-        <ns0:v>420</ns0:v>
-      </ns0:c>
-      <ns0:c r="E15" s="1" t="n">
-        <ns0:v>413.35</ns0:v>
-      </ns0:c>
+      <ns0:c r="D15" s="1"/>
+      <ns0:c r="E15" s="1"/>
       <ns0:c r="F15" s="1" t="n">
         <ns0:v>0</ns0:v>
       </ns0:c>
@@ -5017,9 +4935,7 @@
       <ns0:c r="P15" s="1" t="n">
         <ns0:v>64</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q15" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q15"/>
     </ns0:row>
     <ns0:row r="16" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A16" s="6" t="n">
@@ -5031,12 +4947,8 @@
       <ns0:c r="C16" s="1" t="n">
         <ns0:v>4</ns0:v>
       </ns0:c>
-      <ns0:c r="D16" s="1" t="n">
-        <ns0:v>420</ns0:v>
-      </ns0:c>
-      <ns0:c r="E16" s="1" t="n">
-        <ns0:v>410.67</ns0:v>
-      </ns0:c>
+      <ns0:c r="D16" s="1"/>
+      <ns0:c r="E16" s="1"/>
       <ns0:c r="F16" s="1" t="n">
         <ns0:v>0</ns0:v>
       </ns0:c>
@@ -5070,9 +4982,7 @@
       <ns0:c r="P16" s="1" t="n">
         <ns0:v>64</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q16" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q16"/>
     </ns0:row>
     <ns0:row r="17" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A17" s="6" t="n">
@@ -5084,12 +4994,8 @@
       <ns0:c r="C17" s="1" t="n">
         <ns0:v>4</ns0:v>
       </ns0:c>
-      <ns0:c r="D17" s="1" t="n">
-        <ns0:v>420</ns0:v>
-      </ns0:c>
-      <ns0:c r="E17" s="1" t="n">
-        <ns0:v>415.25</ns0:v>
-      </ns0:c>
+      <ns0:c r="D17" s="1"/>
+      <ns0:c r="E17" s="1"/>
       <ns0:c r="F17" s="1" t="n">
         <ns0:v>0</ns0:v>
       </ns0:c>
@@ -5123,9 +5029,7 @@
       <ns0:c r="P17" s="1" t="n">
         <ns0:v>64</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q17" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q17"/>
     </ns0:row>
     <ns0:row r="18" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A18" s="6" t="n">
@@ -5137,12 +5041,8 @@
       <ns0:c r="C18" s="1" t="n">
         <ns0:v>5</ns0:v>
       </ns0:c>
-      <ns0:c r="D18" s="1" t="n">
-        <ns0:v>434.47</ns0:v>
-      </ns0:c>
-      <ns0:c r="E18" s="1" t="n">
-        <ns0:v>410.89</ns0:v>
-      </ns0:c>
+      <ns0:c r="D18" s="1"/>
+      <ns0:c r="E18" s="1"/>
       <ns0:c r="F18" s="1" t="n">
         <ns0:v>180</ns0:v>
       </ns0:c>
@@ -5176,9 +5076,7 @@
       <ns0:c r="P18" s="1" t="n">
         <ns0:v>64</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q18" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q18"/>
     </ns0:row>
     <ns0:row r="19" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A19" s="6" t="n">
@@ -5190,12 +5088,8 @@
       <ns0:c r="C19" s="1" t="n">
         <ns0:v>5</ns0:v>
       </ns0:c>
-      <ns0:c r="D19" s="1" t="n">
-        <ns0:v>434.47</ns0:v>
-      </ns0:c>
-      <ns0:c r="E19" s="1" t="n">
-        <ns0:v>411.83</ns0:v>
-      </ns0:c>
+      <ns0:c r="D19" s="1"/>
+      <ns0:c r="E19" s="1"/>
       <ns0:c r="F19" s="1" t="n">
         <ns0:v>300</ns0:v>
       </ns0:c>
@@ -5229,9 +5123,7 @@
       <ns0:c r="P19" s="1" t="n">
         <ns0:v>64</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q19" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q19"/>
     </ns0:row>
     <ns0:row r="20" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A20" s="6" t="n">
@@ -5243,12 +5135,8 @@
       <ns0:c r="C20" s="1" t="n">
         <ns0:v>5</ns0:v>
       </ns0:c>
-      <ns0:c r="D20" s="1" t="n">
-        <ns0:v>434.47</ns0:v>
-      </ns0:c>
-      <ns0:c r="E20" s="1" t="n">
-        <ns0:v>410</ns0:v>
-      </ns0:c>
+      <ns0:c r="D20" s="1"/>
+      <ns0:c r="E20" s="1"/>
       <ns0:c r="F20" s="1" t="n">
         <ns0:v>640</ns0:v>
       </ns0:c>
@@ -5282,9 +5170,7 @@
       <ns0:c r="P20" s="1" t="n">
         <ns0:v>64</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q20" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q20"/>
     </ns0:row>
     <ns0:row r="21" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A21" s="6" t="n">
@@ -5296,12 +5182,8 @@
       <ns0:c r="C21" s="1" t="n">
         <ns0:v>5</ns0:v>
       </ns0:c>
-      <ns0:c r="D21" s="1" t="n">
-        <ns0:v>434.47</ns0:v>
-      </ns0:c>
-      <ns0:c r="E21" s="1" t="n">
-        <ns0:v>390.38</ns0:v>
-      </ns0:c>
+      <ns0:c r="D21" s="1"/>
+      <ns0:c r="E21" s="1"/>
       <ns0:c r="F21" s="1" t="n">
         <ns0:v>780</ns0:v>
       </ns0:c>
@@ -5335,9 +5217,7 @@
       <ns0:c r="P21" s="1" t="n">
         <ns0:v>64</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q21" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q21"/>
     </ns0:row>
     <ns0:row r="22" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A22" s="6" t="n">
@@ -5349,12 +5229,8 @@
       <ns0:c r="C22" s="1" t="n">
         <ns0:v>6</ns0:v>
       </ns0:c>
-      <ns0:c r="D22" s="1" t="n">
-        <ns0:v>446.76</ns0:v>
-      </ns0:c>
-      <ns0:c r="E22" s="1" t="n">
-        <ns0:v>370</ns0:v>
-      </ns0:c>
+      <ns0:c r="D22" s="1"/>
+      <ns0:c r="E22" s="1"/>
       <ns0:c r="F22" s="1" t="n">
         <ns0:v>1320</ns0:v>
       </ns0:c>
@@ -5388,9 +5264,7 @@
       <ns0:c r="P22" s="1" t="n">
         <ns0:v>64</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q22" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q22"/>
     </ns0:row>
     <ns0:row r="23" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A23" s="6" t="n">
@@ -5402,12 +5276,8 @@
       <ns0:c r="C23" s="1" t="n">
         <ns0:v>6</ns0:v>
       </ns0:c>
-      <ns0:c r="D23" s="1" t="n">
-        <ns0:v>446.76</ns0:v>
-      </ns0:c>
-      <ns0:c r="E23" s="1" t="n">
-        <ns0:v>358.07</ns0:v>
-      </ns0:c>
+      <ns0:c r="D23" s="1"/>
+      <ns0:c r="E23" s="1"/>
       <ns0:c r="F23" s="1" t="n">
         <ns0:v>1810</ns0:v>
       </ns0:c>
@@ -5441,9 +5311,7 @@
       <ns0:c r="P23" s="1" t="n">
         <ns0:v>64</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q23" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q23"/>
     </ns0:row>
     <ns0:row r="24" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A24" s="6" t="n">
@@ -5455,12 +5323,8 @@
       <ns0:c r="C24" s="1" t="n">
         <ns0:v>6</ns0:v>
       </ns0:c>
-      <ns0:c r="D24" s="1" t="n">
-        <ns0:v>446.76</ns0:v>
-      </ns0:c>
-      <ns0:c r="E24" s="1" t="n">
-        <ns0:v>353.54</ns0:v>
-      </ns0:c>
+      <ns0:c r="D24" s="1"/>
+      <ns0:c r="E24" s="1"/>
       <ns0:c r="F24" s="1" t="n">
         <ns0:v>2030</ns0:v>
       </ns0:c>
@@ -5494,9 +5358,7 @@
       <ns0:c r="P24" s="1" t="n">
         <ns0:v>64</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q24" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q24"/>
     </ns0:row>
     <ns0:row r="25" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A25" s="6" t="n">
@@ -5508,12 +5370,8 @@
       <ns0:c r="C25" s="1" t="n">
         <ns0:v>6</ns0:v>
       </ns0:c>
-      <ns0:c r="D25" s="1" t="n">
-        <ns0:v>446.76</ns0:v>
-      </ns0:c>
-      <ns0:c r="E25" s="1" t="n">
-        <ns0:v>355.48</ns0:v>
-      </ns0:c>
+      <ns0:c r="D25" s="1"/>
+      <ns0:c r="E25" s="1"/>
       <ns0:c r="F25" s="1" t="n">
         <ns0:v>2010</ns0:v>
       </ns0:c>
@@ -5547,9 +5405,7 @@
       <ns0:c r="P25" s="1" t="n">
         <ns0:v>64</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q25" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q25"/>
     </ns0:row>
     <ns0:row r="26" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A26" s="6" t="n">
@@ -5561,12 +5417,8 @@
       <ns0:c r="C26" s="1" t="n">
         <ns0:v>7</ns0:v>
       </ns0:c>
-      <ns0:c r="D26" s="1" t="n">
-        <ns0:v>470</ns0:v>
-      </ns0:c>
-      <ns0:c r="E26" s="1" t="n">
-        <ns0:v>335.98</ns0:v>
-      </ns0:c>
+      <ns0:c r="D26" s="1"/>
+      <ns0:c r="E26" s="1"/>
       <ns0:c r="F26" s="1" t="n">
         <ns0:v>2320</ns0:v>
       </ns0:c>
@@ -5600,9 +5452,7 @@
       <ns0:c r="P26" s="1" t="n">
         <ns0:v>65</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q26" t="n">
-        <ns0:v>0</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q26"/>
     </ns0:row>
     <ns0:row r="27" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A27" s="6" t="n">
@@ -5614,12 +5464,8 @@
       <ns0:c r="C27" s="1" t="n">
         <ns0:v>7</ns0:v>
       </ns0:c>
-      <ns0:c r="D27" s="1" t="n">
-        <ns0:v>470</ns0:v>
-      </ns0:c>
-      <ns0:c r="E27" s="1" t="n">
-        <ns0:v>350.91</ns0:v>
-      </ns0:c>
+      <ns0:c r="D27" s="1"/>
+      <ns0:c r="E27" s="1"/>
       <ns0:c r="F27" s="1" t="n">
         <ns0:v>2305</ns0:v>
       </ns0:c>
@@ -5653,9 +5499,7 @@
       <ns0:c r="P27" s="1" t="n">
         <ns0:v>65</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q27" t="n">
-        <ns0:v>0</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q27"/>
     </ns0:row>
     <ns0:row r="28" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A28" s="6" t="n">
@@ -5667,12 +5511,8 @@
       <ns0:c r="C28" s="1" t="n">
         <ns0:v>7</ns0:v>
       </ns0:c>
-      <ns0:c r="D28" s="1" t="n">
-        <ns0:v>470</ns0:v>
-      </ns0:c>
-      <ns0:c r="E28" s="1" t="n">
-        <ns0:v>414.04</ns0:v>
-      </ns0:c>
+      <ns0:c r="D28" s="1"/>
+      <ns0:c r="E28" s="1"/>
       <ns0:c r="F28" s="1" t="n">
         <ns0:v>1975</ns0:v>
       </ns0:c>
@@ -5706,9 +5546,7 @@
       <ns0:c r="P28" s="1" t="n">
         <ns0:v>65</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q28" t="n">
-        <ns0:v>0</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q28"/>
     </ns0:row>
     <ns0:row r="29" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A29" s="6" t="n">
@@ -5720,12 +5558,8 @@
       <ns0:c r="C29" s="1" t="n">
         <ns0:v>7</ns0:v>
       </ns0:c>
-      <ns0:c r="D29" s="1" t="n">
-        <ns0:v>470</ns0:v>
-      </ns0:c>
-      <ns0:c r="E29" s="1" t="n">
-        <ns0:v>430.14</ns0:v>
-      </ns0:c>
+      <ns0:c r="D29" s="1"/>
+      <ns0:c r="E29" s="1"/>
       <ns0:c r="F29" s="1" t="n">
         <ns0:v>1655</ns0:v>
       </ns0:c>
@@ -5759,9 +5593,7 @@
       <ns0:c r="P29" s="1" t="n">
         <ns0:v>65</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q29" t="n">
-        <ns0:v>0</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q29"/>
     </ns0:row>
     <ns0:row r="30" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A30" s="6" t="n">
@@ -5773,12 +5605,8 @@
       <ns0:c r="C30" s="1" t="n">
         <ns0:v>8</ns0:v>
       </ns0:c>
-      <ns0:c r="D30" s="1" t="n">
-        <ns0:v>420</ns0:v>
-      </ns0:c>
-      <ns0:c r="E30" s="1" t="n">
-        <ns0:v>445</ns0:v>
-      </ns0:c>
+      <ns0:c r="D30" s="1"/>
+      <ns0:c r="E30" s="1"/>
       <ns0:c r="F30" s="1" t="n">
         <ns0:v>980</ns0:v>
       </ns0:c>
@@ -5812,9 +5640,7 @@
       <ns0:c r="P30" s="1" t="n">
         <ns0:v>65</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q30" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q30"/>
     </ns0:row>
     <ns0:row r="31" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A31" s="6" t="n">
@@ -5826,12 +5652,8 @@
       <ns0:c r="C31" s="1" t="n">
         <ns0:v>8</ns0:v>
       </ns0:c>
-      <ns0:c r="D31" s="1" t="n">
-        <ns0:v>420</ns0:v>
-      </ns0:c>
-      <ns0:c r="E31" s="1" t="n">
-        <ns0:v>434.35</ns0:v>
-      </ns0:c>
+      <ns0:c r="D31" s="1"/>
+      <ns0:c r="E31" s="1"/>
       <ns0:c r="F31" s="1" t="n">
         <ns0:v>694</ns0:v>
       </ns0:c>
@@ -5865,9 +5687,7 @@
       <ns0:c r="P31" s="1" t="n">
         <ns0:v>65</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q31" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q31"/>
     </ns0:row>
     <ns0:row r="32" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A32" s="6" t="n">
@@ -5879,12 +5699,8 @@
       <ns0:c r="C32" s="1" t="n">
         <ns0:v>8</ns0:v>
       </ns0:c>
-      <ns0:c r="D32" s="1" t="n">
-        <ns0:v>420</ns0:v>
-      </ns0:c>
-      <ns0:c r="E32" s="1" t="n">
-        <ns0:v>425.45</ns0:v>
-      </ns0:c>
+      <ns0:c r="D32" s="1"/>
+      <ns0:c r="E32" s="1"/>
       <ns0:c r="F32" s="1" t="n">
         <ns0:v>155</ns0:v>
       </ns0:c>
@@ -5918,9 +5734,7 @@
       <ns0:c r="P32" s="1" t="n">
         <ns0:v>65</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q32" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q32"/>
     </ns0:row>
     <ns0:row r="33" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A33" s="6" t="n">
@@ -5932,12 +5746,8 @@
       <ns0:c r="C33" s="1" t="n">
         <ns0:v>8</ns0:v>
       </ns0:c>
-      <ns0:c r="D33" s="1" t="n">
-        <ns0:v>420</ns0:v>
-      </ns0:c>
-      <ns0:c r="E33" s="1" t="n">
-        <ns0:v>409.66</ns0:v>
-      </ns0:c>
+      <ns0:c r="D33" s="1"/>
+      <ns0:c r="E33" s="1"/>
       <ns0:c r="F33" s="1" t="n">
         <ns0:v>40</ns0:v>
       </ns0:c>
@@ -5971,9 +5781,7 @@
       <ns0:c r="P33" s="1" t="n">
         <ns0:v>65</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q33" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q33"/>
     </ns0:row>
     <ns0:row r="34" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A34" s="6" t="n">
@@ -5985,12 +5793,8 @@
       <ns0:c r="C34" s="1" t="n">
         <ns0:v>9</ns0:v>
       </ns0:c>
-      <ns0:c r="D34" s="1" t="n">
-        <ns0:v>415.25</ns0:v>
-      </ns0:c>
-      <ns0:c r="E34" s="1" t="n">
-        <ns0:v>395.97</ns0:v>
-      </ns0:c>
+      <ns0:c r="D34" s="1"/>
+      <ns0:c r="E34" s="1"/>
       <ns0:c r="F34" s="1" t="n">
         <ns0:v>0</ns0:v>
       </ns0:c>
@@ -6024,9 +5828,7 @@
       <ns0:c r="P34" s="1" t="n">
         <ns0:v>65</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q34" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q34"/>
     </ns0:row>
     <ns0:row r="35" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A35" s="6" t="n">
@@ -6038,12 +5840,8 @@
       <ns0:c r="C35" s="1" t="n">
         <ns0:v>9</ns0:v>
       </ns0:c>
-      <ns0:c r="D35" s="1" t="n">
-        <ns0:v>415.25</ns0:v>
-      </ns0:c>
-      <ns0:c r="E35" s="1" t="n">
-        <ns0:v>353.51</ns0:v>
-      </ns0:c>
+      <ns0:c r="D35" s="1"/>
+      <ns0:c r="E35" s="1"/>
       <ns0:c r="F35" s="1" t="n">
         <ns0:v>0</ns0:v>
       </ns0:c>
@@ -6077,9 +5875,7 @@
       <ns0:c r="P35" s="1" t="n">
         <ns0:v>65</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q35" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q35"/>
     </ns0:row>
     <ns0:row r="36" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A36" s="6" t="n">
@@ -6091,12 +5887,8 @@
       <ns0:c r="C36" s="1" t="n">
         <ns0:v>9</ns0:v>
       </ns0:c>
-      <ns0:c r="D36" s="1" t="n">
-        <ns0:v>415.25</ns0:v>
-      </ns0:c>
-      <ns0:c r="E36" s="1" t="n">
-        <ns0:v>350.26</ns0:v>
-      </ns0:c>
+      <ns0:c r="D36" s="1"/>
+      <ns0:c r="E36" s="1"/>
       <ns0:c r="F36" s="1" t="n">
         <ns0:v>0</ns0:v>
       </ns0:c>
@@ -6130,9 +5922,7 @@
       <ns0:c r="P36" s="1" t="n">
         <ns0:v>65</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q36" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q36"/>
     </ns0:row>
     <ns0:row r="37" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A37" s="6" t="n">
@@ -6144,12 +5934,8 @@
       <ns0:c r="C37" s="1" t="n">
         <ns0:v>9</ns0:v>
       </ns0:c>
-      <ns0:c r="D37" s="1" t="n">
-        <ns0:v>415.25</ns0:v>
-      </ns0:c>
-      <ns0:c r="E37" s="1" t="n">
-        <ns0:v>276.08</ns0:v>
-      </ns0:c>
+      <ns0:c r="D37" s="1"/>
+      <ns0:c r="E37" s="1"/>
       <ns0:c r="F37" s="1" t="n">
         <ns0:v>0</ns0:v>
       </ns0:c>
@@ -6183,9 +5969,7 @@
       <ns0:c r="P37" s="1" t="n">
         <ns0:v>65</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q37" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q37"/>
     </ns0:row>
     <ns0:row r="38" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A38" s="6" t="n">
@@ -6197,12 +5981,8 @@
       <ns0:c r="C38" s="1" t="n">
         <ns0:v>10</ns0:v>
       </ns0:c>
-      <ns0:c r="D38" s="1" t="n">
-        <ns0:v>234.16</ns0:v>
-      </ns0:c>
-      <ns0:c r="E38" s="1" t="n">
-        <ns0:v>186.94</ns0:v>
-      </ns0:c>
+      <ns0:c r="D38" s="1"/>
+      <ns0:c r="E38" s="1"/>
       <ns0:c r="F38" s="1" t="n">
         <ns0:v>-84</ns0:v>
       </ns0:c>
@@ -6236,9 +6016,7 @@
       <ns0:c r="P38" s="1" t="n">
         <ns0:v>65</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q38" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q38"/>
     </ns0:row>
     <ns0:row r="39" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A39" s="6" t="n">
@@ -6250,12 +6028,8 @@
       <ns0:c r="C39" s="1" t="n">
         <ns0:v>10</ns0:v>
       </ns0:c>
-      <ns0:c r="D39" s="1" t="n">
-        <ns0:v>234.16</ns0:v>
-      </ns0:c>
-      <ns0:c r="E39" s="1" t="n">
-        <ns0:v>182.88</ns0:v>
-      </ns0:c>
+      <ns0:c r="D39" s="1"/>
+      <ns0:c r="E39" s="1"/>
       <ns0:c r="F39" s="1" t="n">
         <ns0:v>-220</ns0:v>
       </ns0:c>
@@ -6289,9 +6063,7 @@
       <ns0:c r="P39" s="1" t="n">
         <ns0:v>65</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q39" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q39"/>
     </ns0:row>
     <ns0:row r="40" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A40" s="6" t="n">
@@ -6303,12 +6075,8 @@
       <ns0:c r="C40" s="1" t="n">
         <ns0:v>10</ns0:v>
       </ns0:c>
-      <ns0:c r="D40" s="1" t="n">
-        <ns0:v>234.16</ns0:v>
-      </ns0:c>
-      <ns0:c r="E40" s="1" t="n">
-        <ns0:v>184.11</ns0:v>
-      </ns0:c>
+      <ns0:c r="D40" s="1"/>
+      <ns0:c r="E40" s="1"/>
       <ns0:c r="F40" s="1" t="n">
         <ns0:v>-416</ns0:v>
       </ns0:c>
@@ -6342,9 +6110,7 @@
       <ns0:c r="P40" s="1" t="n">
         <ns0:v>65</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q40" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q40"/>
     </ns0:row>
     <ns0:row r="41" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A41" s="6" t="n">
@@ -6356,12 +6122,8 @@
       <ns0:c r="C41" s="1" t="n">
         <ns0:v>10</ns0:v>
       </ns0:c>
-      <ns0:c r="D41" s="1" t="n">
-        <ns0:v>234.16</ns0:v>
-      </ns0:c>
-      <ns0:c r="E41" s="1" t="n">
-        <ns0:v>177.47</ns0:v>
-      </ns0:c>
+      <ns0:c r="D41" s="1"/>
+      <ns0:c r="E41" s="1"/>
       <ns0:c r="F41" s="1" t="n">
         <ns0:v>-492.5</ns0:v>
       </ns0:c>
@@ -6395,9 +6157,7 @@
       <ns0:c r="P41" s="1" t="n">
         <ns0:v>65</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q41" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q41"/>
     </ns0:row>
     <ns0:row r="42" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A42" s="6" t="n">
@@ -6409,12 +6169,8 @@
       <ns0:c r="C42" s="1" t="n">
         <ns0:v>11</ns0:v>
       </ns0:c>
-      <ns0:c r="D42" s="1" t="n">
-        <ns0:v>155.22</ns0:v>
-      </ns0:c>
-      <ns0:c r="E42" s="1" t="n">
-        <ns0:v>178.71</ns0:v>
-      </ns0:c>
+      <ns0:c r="D42" s="1"/>
+      <ns0:c r="E42" s="1"/>
       <ns0:c r="F42" s="1" t="n">
         <ns0:v>-885.5</ns0:v>
       </ns0:c>
@@ -6448,9 +6204,7 @@
       <ns0:c r="P42" s="1" t="n">
         <ns0:v>65</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q42" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q42"/>
     </ns0:row>
     <ns0:row r="43" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A43" s="6" t="n">
@@ -6462,12 +6216,8 @@
       <ns0:c r="C43" s="1" t="n">
         <ns0:v>11</ns0:v>
       </ns0:c>
-      <ns0:c r="D43" s="1" t="n">
-        <ns0:v>155.22</ns0:v>
-      </ns0:c>
-      <ns0:c r="E43" s="1" t="n">
-        <ns0:v>175.52</ns0:v>
-      </ns0:c>
+      <ns0:c r="D43" s="1"/>
+      <ns0:c r="E43" s="1"/>
       <ns0:c r="F43" s="1" t="n">
         <ns0:v>-1026</ns0:v>
       </ns0:c>
@@ -6501,9 +6251,7 @@
       <ns0:c r="P43" s="1" t="n">
         <ns0:v>65</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q43" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q43"/>
     </ns0:row>
     <ns0:row r="44" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A44" s="6" t="n">
@@ -6515,12 +6263,8 @@
       <ns0:c r="C44" s="1" t="n">
         <ns0:v>11</ns0:v>
       </ns0:c>
-      <ns0:c r="D44" s="1" t="n">
-        <ns0:v>155.22</ns0:v>
-      </ns0:c>
-      <ns0:c r="E44" s="1" t="n">
-        <ns0:v>172.96</ns0:v>
-      </ns0:c>
+      <ns0:c r="D44" s="1"/>
+      <ns0:c r="E44" s="1"/>
       <ns0:c r="F44" s="1" t="n">
         <ns0:v>-1126</ns0:v>
       </ns0:c>
@@ -6554,9 +6298,7 @@
       <ns0:c r="P44" s="1" t="n">
         <ns0:v>65</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q44" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q44"/>
     </ns0:row>
     <ns0:row r="45" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A45" s="6" t="n">
@@ -6568,12 +6310,8 @@
       <ns0:c r="C45" s="1" t="n">
         <ns0:v>11</ns0:v>
       </ns0:c>
-      <ns0:c r="D45" s="1" t="n">
-        <ns0:v>155.22</ns0:v>
-      </ns0:c>
-      <ns0:c r="E45" s="1" t="n">
-        <ns0:v>186.94</ns0:v>
-      </ns0:c>
+      <ns0:c r="D45" s="1"/>
+      <ns0:c r="E45" s="1"/>
       <ns0:c r="F45" s="1" t="n">
         <ns0:v>-1121</ns0:v>
       </ns0:c>
@@ -6607,9 +6345,7 @@
       <ns0:c r="P45" s="1" t="n">
         <ns0:v>65</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q45" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q45"/>
     </ns0:row>
     <ns0:row r="46" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A46" s="6" t="n">
@@ -6621,12 +6357,8 @@
       <ns0:c r="C46" s="1" t="n">
         <ns0:v>12</ns0:v>
       </ns0:c>
-      <ns0:c r="D46" s="1" t="n">
-        <ns0:v>234.16</ns0:v>
-      </ns0:c>
-      <ns0:c r="E46" s="1" t="n">
-        <ns0:v>210</ns0:v>
-      </ns0:c>
+      <ns0:c r="D46" s="1"/>
+      <ns0:c r="E46" s="1"/>
       <ns0:c r="F46" s="1" t="n">
         <ns0:v>-1046</ns0:v>
       </ns0:c>
@@ -6660,9 +6392,7 @@
       <ns0:c r="P46" s="1" t="n">
         <ns0:v>65</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q46" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q46"/>
     </ns0:row>
     <ns0:row r="47" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A47" s="6" t="n">
@@ -6674,12 +6404,8 @@
       <ns0:c r="C47" s="1" t="n">
         <ns0:v>12</ns0:v>
       </ns0:c>
-      <ns0:c r="D47" s="1" t="n">
-        <ns0:v>234.16</ns0:v>
-      </ns0:c>
-      <ns0:c r="E47" s="1" t="n">
-        <ns0:v>274.6</ns0:v>
-      </ns0:c>
+      <ns0:c r="D47" s="1"/>
+      <ns0:c r="E47" s="1"/>
       <ns0:c r="F47" s="1" t="n">
         <ns0:v>-1046</ns0:v>
       </ns0:c>
@@ -6713,9 +6439,7 @@
       <ns0:c r="P47" s="1" t="n">
         <ns0:v>65</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q47" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q47"/>
     </ns0:row>
     <ns0:row r="48" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A48" s="6" t="n">
@@ -6727,12 +6451,8 @@
       <ns0:c r="C48" s="1" t="n">
         <ns0:v>12</ns0:v>
       </ns0:c>
-      <ns0:c r="D48" s="1" t="n">
-        <ns0:v>234.16</ns0:v>
-      </ns0:c>
-      <ns0:c r="E48" s="1" t="n">
-        <ns0:v>210</ns0:v>
-      </ns0:c>
+      <ns0:c r="D48" s="1"/>
+      <ns0:c r="E48" s="1"/>
       <ns0:c r="F48" s="1" t="n">
         <ns0:v>-1046</ns0:v>
       </ns0:c>
@@ -6766,9 +6486,7 @@
       <ns0:c r="P48" s="1" t="n">
         <ns0:v>65</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q48" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q48"/>
     </ns0:row>
     <ns0:row r="49" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A49" s="6" t="n">
@@ -6780,12 +6498,8 @@
       <ns0:c r="C49" s="1" t="n">
         <ns0:v>12</ns0:v>
       </ns0:c>
-      <ns0:c r="D49" s="1" t="n">
-        <ns0:v>234.16</ns0:v>
-      </ns0:c>
-      <ns0:c r="E49" s="1" t="n">
-        <ns0:v>204.16</ns0:v>
-      </ns0:c>
+      <ns0:c r="D49" s="1"/>
+      <ns0:c r="E49" s="1"/>
       <ns0:c r="F49" s="1" t="n">
         <ns0:v>-1026</ns0:v>
       </ns0:c>
@@ -6819,9 +6533,7 @@
       <ns0:c r="P49" s="1" t="n">
         <ns0:v>65</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q49" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q49"/>
     </ns0:row>
     <ns0:row r="50" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A50" s="6" t="n">
@@ -6833,12 +6545,8 @@
       <ns0:c r="C50" s="1" t="n">
         <ns0:v>13</ns0:v>
       </ns0:c>
-      <ns0:c r="D50" s="1" t="n">
-        <ns0:v>149.52</ns0:v>
-      </ns0:c>
-      <ns0:c r="E50" s="1" t="n">
-        <ns0:v>200.77</ns0:v>
-      </ns0:c>
+      <ns0:c r="D50" s="1"/>
+      <ns0:c r="E50" s="1"/>
       <ns0:c r="F50" s="1" t="n">
         <ns0:v>-951</ns0:v>
       </ns0:c>
@@ -6872,9 +6580,7 @@
       <ns0:c r="P50" s="1" t="n">
         <ns0:v>65</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q50" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q50"/>
     </ns0:row>
     <ns0:row r="51" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A51" s="6" t="n">
@@ -6886,12 +6592,8 @@
       <ns0:c r="C51" s="1" t="n">
         <ns0:v>13</ns0:v>
       </ns0:c>
-      <ns0:c r="D51" s="1" t="n">
-        <ns0:v>149.52</ns0:v>
-      </ns0:c>
-      <ns0:c r="E51" s="1" t="n">
-        <ns0:v>186.94</ns0:v>
-      </ns0:c>
+      <ns0:c r="D51" s="1"/>
+      <ns0:c r="E51" s="1"/>
       <ns0:c r="F51" s="1" t="n">
         <ns0:v>-803</ns0:v>
       </ns0:c>
@@ -6925,9 +6627,7 @@
       <ns0:c r="P51" s="1" t="n">
         <ns0:v>65</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q51" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q51"/>
     </ns0:row>
     <ns0:row r="52" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A52" s="6" t="n">
@@ -6939,12 +6639,8 @@
       <ns0:c r="C52" s="1" t="n">
         <ns0:v>13</ns0:v>
       </ns0:c>
-      <ns0:c r="D52" s="1" t="n">
-        <ns0:v>149.52</ns0:v>
-      </ns0:c>
-      <ns0:c r="E52" s="1" t="n">
-        <ns0:v>206.47</ns0:v>
-      </ns0:c>
+      <ns0:c r="D52" s="1"/>
+      <ns0:c r="E52" s="1"/>
       <ns0:c r="F52" s="1" t="n">
         <ns0:v>-724</ns0:v>
       </ns0:c>
@@ -6978,9 +6674,7 @@
       <ns0:c r="P52" s="1" t="n">
         <ns0:v>65</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q52" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q52"/>
     </ns0:row>
     <ns0:row r="53" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A53" s="6" t="n">
@@ -6992,12 +6686,8 @@
       <ns0:c r="C53" s="1" t="n">
         <ns0:v>13</ns0:v>
       </ns0:c>
-      <ns0:c r="D53" s="1" t="n">
-        <ns0:v>149.52</ns0:v>
-      </ns0:c>
-      <ns0:c r="E53" s="1" t="n">
-        <ns0:v>200.57</ns0:v>
-      </ns0:c>
+      <ns0:c r="D53" s="1"/>
+      <ns0:c r="E53" s="1"/>
       <ns0:c r="F53" s="1" t="n">
         <ns0:v>-689</ns0:v>
       </ns0:c>
@@ -7031,9 +6721,7 @@
       <ns0:c r="P53" s="1" t="n">
         <ns0:v>65</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q53" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q53"/>
     </ns0:row>
     <ns0:row r="54" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A54" s="6" t="n">
@@ -7045,12 +6733,8 @@
       <ns0:c r="C54" s="1" t="n">
         <ns0:v>14</ns0:v>
       </ns0:c>
-      <ns0:c r="D54" s="1" t="n">
-        <ns0:v>155.22</ns0:v>
-      </ns0:c>
-      <ns0:c r="E54" s="1" t="n">
-        <ns0:v>207.16</ns0:v>
-      </ns0:c>
+      <ns0:c r="D54" s="1"/>
+      <ns0:c r="E54" s="1"/>
       <ns0:c r="F54" s="1" t="n">
         <ns0:v>-538</ns0:v>
       </ns0:c>
@@ -7084,9 +6768,7 @@
       <ns0:c r="P54" s="1" t="n">
         <ns0:v>65</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q54" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q54"/>
     </ns0:row>
     <ns0:row r="55" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A55" s="6" t="n">
@@ -7098,12 +6780,8 @@
       <ns0:c r="C55" s="1" t="n">
         <ns0:v>14</ns0:v>
       </ns0:c>
-      <ns0:c r="D55" s="1" t="n">
-        <ns0:v>155.22</ns0:v>
-      </ns0:c>
-      <ns0:c r="E55" s="1" t="n">
-        <ns0:v>244.52</ns0:v>
-      </ns0:c>
+      <ns0:c r="D55" s="1"/>
+      <ns0:c r="E55" s="1"/>
       <ns0:c r="F55" s="1" t="n">
         <ns0:v>-407.5</ns0:v>
       </ns0:c>
@@ -7137,9 +6815,7 @@
       <ns0:c r="P55" s="1" t="n">
         <ns0:v>65</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q55" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q55"/>
     </ns0:row>
     <ns0:row r="56" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A56" s="6" t="n">
@@ -7151,12 +6827,8 @@
       <ns0:c r="C56" s="1" t="n">
         <ns0:v>14</ns0:v>
       </ns0:c>
-      <ns0:c r="D56" s="1" t="n">
-        <ns0:v>155.22</ns0:v>
-      </ns0:c>
-      <ns0:c r="E56" s="1" t="n">
-        <ns0:v>279.92</ns0:v>
-      </ns0:c>
+      <ns0:c r="D56" s="1"/>
+      <ns0:c r="E56" s="1"/>
       <ns0:c r="F56" s="1" t="n">
         <ns0:v>-152.5</ns0:v>
       </ns0:c>
@@ -7190,9 +6862,7 @@
       <ns0:c r="P56" s="1" t="n">
         <ns0:v>65</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q56" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q56"/>
     </ns0:row>
     <ns0:row r="57" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A57" s="6" t="n">
@@ -7204,12 +6874,8 @@
       <ns0:c r="C57" s="1" t="n">
         <ns0:v>14</ns0:v>
       </ns0:c>
-      <ns0:c r="D57" s="1" t="n">
-        <ns0:v>155.22</ns0:v>
-      </ns0:c>
-      <ns0:c r="E57" s="1" t="n">
-        <ns0:v>234.16</ns0:v>
-      </ns0:c>
+      <ns0:c r="D57" s="1"/>
+      <ns0:c r="E57" s="1"/>
       <ns0:c r="F57" s="1" t="n">
         <ns0:v>-30</ns0:v>
       </ns0:c>
@@ -7243,9 +6909,7 @@
       <ns0:c r="P57" s="1" t="n">
         <ns0:v>65</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q57" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q57"/>
     </ns0:row>
     <ns0:row r="58" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A58" s="6" t="n">
@@ -7257,12 +6921,8 @@
       <ns0:c r="C58" s="1" t="n">
         <ns0:v>15</ns0:v>
       </ns0:c>
-      <ns0:c r="D58" s="1" t="n">
-        <ns0:v>369.51</ns0:v>
-      </ns0:c>
-      <ns0:c r="E58" s="1" t="n">
-        <ns0:v>279.07</ns0:v>
-      </ns0:c>
+      <ns0:c r="D58" s="1"/>
+      <ns0:c r="E58" s="1"/>
       <ns0:c r="F58" s="1" t="n">
         <ns0:v>0</ns0:v>
       </ns0:c>
@@ -7296,9 +6956,7 @@
       <ns0:c r="P58" s="1" t="n">
         <ns0:v>65</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q58" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q58"/>
     </ns0:row>
     <ns0:row r="59" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A59" s="6" t="n">
@@ -7310,12 +6968,8 @@
       <ns0:c r="C59" s="1" t="n">
         <ns0:v>15</ns0:v>
       </ns0:c>
-      <ns0:c r="D59" s="1" t="n">
-        <ns0:v>369.35</ns0:v>
-      </ns0:c>
-      <ns0:c r="E59" s="1" t="n">
-        <ns0:v>310.42</ns0:v>
-      </ns0:c>
+      <ns0:c r="D59" s="1"/>
+      <ns0:c r="E59" s="1"/>
       <ns0:c r="F59" s="1" t="n">
         <ns0:v>0</ns0:v>
       </ns0:c>
@@ -7349,9 +7003,7 @@
       <ns0:c r="P59" s="1" t="n">
         <ns0:v>65</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q59" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q59"/>
     </ns0:row>
     <ns0:row r="60" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A60" s="6" t="n">
@@ -7363,12 +7015,8 @@
       <ns0:c r="C60" s="1" t="n">
         <ns0:v>15</ns0:v>
       </ns0:c>
-      <ns0:c r="D60" s="1" t="n">
-        <ns0:v>369.35</ns0:v>
-      </ns0:c>
-      <ns0:c r="E60" s="1" t="n">
-        <ns0:v>350.29</ns0:v>
-      </ns0:c>
+      <ns0:c r="D60" s="1"/>
+      <ns0:c r="E60" s="1"/>
       <ns0:c r="F60" s="1" t="n">
         <ns0:v>0</ns0:v>
       </ns0:c>
@@ -7402,9 +7050,7 @@
       <ns0:c r="P60" s="1" t="n">
         <ns0:v>65</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q60" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q60"/>
     </ns0:row>
     <ns0:row r="61" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A61" s="6" t="n">
@@ -7416,12 +7062,8 @@
       <ns0:c r="C61" s="1" t="n">
         <ns0:v>15</ns0:v>
       </ns0:c>
-      <ns0:c r="D61" s="1" t="n">
-        <ns0:v>369.35</ns0:v>
-      </ns0:c>
-      <ns0:c r="E61" s="1" t="n">
-        <ns0:v>380.95</ns0:v>
-      </ns0:c>
+      <ns0:c r="D61" s="1"/>
+      <ns0:c r="E61" s="1"/>
       <ns0:c r="F61" s="1" t="n">
         <ns0:v>0</ns0:v>
       </ns0:c>
@@ -7455,9 +7097,7 @@
       <ns0:c r="P61" s="1" t="n">
         <ns0:v>65</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q61" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q61"/>
     </ns0:row>
     <ns0:row r="62" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A62" s="6" t="n">
@@ -7469,12 +7109,8 @@
       <ns0:c r="C62" s="1" t="n">
         <ns0:v>16</ns0:v>
       </ns0:c>
-      <ns0:c r="D62" s="1" t="n">
-        <ns0:v>400</ns0:v>
-      </ns0:c>
-      <ns0:c r="E62" s="1" t="n">
-        <ns0:v>402.8</ns0:v>
-      </ns0:c>
+      <ns0:c r="D62" s="1"/>
+      <ns0:c r="E62" s="1"/>
       <ns0:c r="F62" s="1" t="n">
         <ns0:v>0</ns0:v>
       </ns0:c>
@@ -7508,9 +7144,7 @@
       <ns0:c r="P62" s="1" t="n">
         <ns0:v>65</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q62" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q62"/>
     </ns0:row>
     <ns0:row r="63" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A63" s="6" t="n">
@@ -7522,12 +7156,8 @@
       <ns0:c r="C63" s="1" t="n">
         <ns0:v>16</ns0:v>
       </ns0:c>
-      <ns0:c r="D63" s="1" t="n">
-        <ns0:v>415.25</ns0:v>
-      </ns0:c>
-      <ns0:c r="E63" s="1" t="n">
-        <ns0:v>419.7</ns0:v>
-      </ns0:c>
+      <ns0:c r="D63" s="1"/>
+      <ns0:c r="E63" s="1"/>
       <ns0:c r="F63" s="1" t="n">
         <ns0:v>0</ns0:v>
       </ns0:c>
@@ -7561,9 +7191,7 @@
       <ns0:c r="P63" s="1" t="n">
         <ns0:v>65</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q63" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q63"/>
     </ns0:row>
     <ns0:row r="64" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A64" s="6" t="n">
@@ -7575,12 +7203,8 @@
       <ns0:c r="C64" s="1" t="n">
         <ns0:v>16</ns0:v>
       </ns0:c>
-      <ns0:c r="D64" s="1" t="n">
-        <ns0:v>400</ns0:v>
-      </ns0:c>
-      <ns0:c r="E64" s="1" t="n">
-        <ns0:v>449.48</ns0:v>
-      </ns0:c>
+      <ns0:c r="D64" s="1"/>
+      <ns0:c r="E64" s="1"/>
       <ns0:c r="F64" s="1" t="n">
         <ns0:v>0</ns0:v>
       </ns0:c>
@@ -7614,9 +7238,7 @@
       <ns0:c r="P64" s="1" t="n">
         <ns0:v>65</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q64" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q64"/>
     </ns0:row>
     <ns0:row r="65" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A65" s="6" t="n">
@@ -7628,12 +7250,8 @@
       <ns0:c r="C65" s="1" t="n">
         <ns0:v>16</ns0:v>
       </ns0:c>
-      <ns0:c r="D65" s="1" t="n">
-        <ns0:v>400</ns0:v>
-      </ns0:c>
-      <ns0:c r="E65" s="1" t="n">
-        <ns0:v>434.2</ns0:v>
-      </ns0:c>
+      <ns0:c r="D65" s="1"/>
+      <ns0:c r="E65" s="1"/>
       <ns0:c r="F65" s="1" t="n">
         <ns0:v>0</ns0:v>
       </ns0:c>
@@ -7667,9 +7285,7 @@
       <ns0:c r="P65" s="1" t="n">
         <ns0:v>65</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q65" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q65"/>
     </ns0:row>
     <ns0:row r="66" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A66" s="6" t="n">
@@ -7681,12 +7297,8 @@
       <ns0:c r="C66" s="1" t="n">
         <ns0:v>17</ns0:v>
       </ns0:c>
-      <ns0:c r="D66" s="1" t="n">
-        <ns0:v>390.94</ns0:v>
-      </ns0:c>
-      <ns0:c r="E66" s="1" t="n">
-        <ns0:v>453.39</ns0:v>
-      </ns0:c>
+      <ns0:c r="D66" s="1"/>
+      <ns0:c r="E66" s="1"/>
       <ns0:c r="F66" s="1" t="n">
         <ns0:v>120</ns0:v>
       </ns0:c>
@@ -7720,9 +7332,7 @@
       <ns0:c r="P66" s="1" t="n">
         <ns0:v>65</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q66" t="n">
-        <ns0:v>0</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q66"/>
     </ns0:row>
     <ns0:row r="67" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A67" s="6" t="n">
@@ -7734,12 +7344,8 @@
       <ns0:c r="C67" s="1" t="n">
         <ns0:v>17</ns0:v>
       </ns0:c>
-      <ns0:c r="D67" s="1" t="n">
-        <ns0:v>390.54</ns0:v>
-      </ns0:c>
-      <ns0:c r="E67" s="1" t="n">
-        <ns0:v>445.91</ns0:v>
-      </ns0:c>
+      <ns0:c r="D67" s="1"/>
+      <ns0:c r="E67" s="1"/>
       <ns0:c r="F67" s="1" t="n">
         <ns0:v>272.5</ns0:v>
       </ns0:c>
@@ -7773,9 +7379,7 @@
       <ns0:c r="P67" s="1" t="n">
         <ns0:v>65</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q67" t="n">
-        <ns0:v>0</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q67"/>
     </ns0:row>
     <ns0:row r="68" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A68" s="6" t="n">
@@ -7787,12 +7391,8 @@
       <ns0:c r="C68" s="1" t="n">
         <ns0:v>17</ns0:v>
       </ns0:c>
-      <ns0:c r="D68" s="1" t="n">
-        <ns0:v>390.54</ns0:v>
-      </ns0:c>
-      <ns0:c r="E68" s="1" t="n">
-        <ns0:v>460</ns0:v>
-      </ns0:c>
+      <ns0:c r="D68" s="1"/>
+      <ns0:c r="E68" s="1"/>
       <ns0:c r="F68" s="1" t="n">
         <ns0:v>607.5</ns0:v>
       </ns0:c>
@@ -7826,9 +7426,7 @@
       <ns0:c r="P68" s="1" t="n">
         <ns0:v>65</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q68" t="n">
-        <ns0:v>0</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q68"/>
     </ns0:row>
     <ns0:row r="69" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A69" s="6" t="n">
@@ -7840,12 +7438,8 @@
       <ns0:c r="C69" s="1" t="n">
         <ns0:v>17</ns0:v>
       </ns0:c>
-      <ns0:c r="D69" s="1" t="n">
-        <ns0:v>390.54</ns0:v>
-      </ns0:c>
-      <ns0:c r="E69" s="1" t="n">
-        <ns0:v>433.64</ns0:v>
-      </ns0:c>
+      <ns0:c r="D69" s="1"/>
+      <ns0:c r="E69" s="1"/>
       <ns0:c r="F69" s="1" t="n">
         <ns0:v>670</ns0:v>
       </ns0:c>
@@ -7879,9 +7473,7 @@
       <ns0:c r="P69" s="1" t="n">
         <ns0:v>65</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q69" t="n">
-        <ns0:v>0</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q69"/>
     </ns0:row>
     <ns0:row r="70" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A70" s="6" t="n">
@@ -7893,12 +7485,8 @@
       <ns0:c r="C70" s="1" t="n">
         <ns0:v>18</ns0:v>
       </ns0:c>
-      <ns0:c r="D70" s="1" t="n">
-        <ns0:v>435.04</ns0:v>
-      </ns0:c>
-      <ns0:c r="E70" s="1" t="n">
-        <ns0:v>413.82</ns0:v>
-      </ns0:c>
+      <ns0:c r="D70" s="1"/>
+      <ns0:c r="E70" s="1"/>
       <ns0:c r="F70" s="1" t="n">
         <ns0:v>755</ns0:v>
       </ns0:c>
@@ -7932,9 +7520,7 @@
       <ns0:c r="P70" s="1" t="n">
         <ns0:v>65</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q70" t="n">
-        <ns0:v>0</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q70"/>
     </ns0:row>
     <ns0:row r="71" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A71" s="6" t="n">
@@ -7946,12 +7532,8 @@
       <ns0:c r="C71" s="1" t="n">
         <ns0:v>18</ns0:v>
       </ns0:c>
-      <ns0:c r="D71" s="1" t="n">
-        <ns0:v>435.04</ns0:v>
-      </ns0:c>
-      <ns0:c r="E71" s="1" t="n">
-        <ns0:v>413.35</ns0:v>
-      </ns0:c>
+      <ns0:c r="D71" s="1"/>
+      <ns0:c r="E71" s="1"/>
       <ns0:c r="F71" s="1" t="n">
         <ns0:v>794</ns0:v>
       </ns0:c>
@@ -7985,9 +7567,7 @@
       <ns0:c r="P71" s="1" t="n">
         <ns0:v>65</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q71" t="n">
-        <ns0:v>0</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q71"/>
     </ns0:row>
     <ns0:row r="72" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A72" s="6" t="n">
@@ -7999,12 +7579,8 @@
       <ns0:c r="C72" s="1" t="n">
         <ns0:v>18</ns0:v>
       </ns0:c>
-      <ns0:c r="D72" s="1" t="n">
-        <ns0:v>435.04</ns0:v>
-      </ns0:c>
-      <ns0:c r="E72" s="1" t="n">
-        <ns0:v>411.01</ns0:v>
-      </ns0:c>
+      <ns0:c r="D72" s="1"/>
+      <ns0:c r="E72" s="1"/>
       <ns0:c r="F72" s="1" t="n">
         <ns0:v>833</ns0:v>
       </ns0:c>
@@ -8038,9 +7614,7 @@
       <ns0:c r="P72" s="1" t="n">
         <ns0:v>65</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q72" t="n">
-        <ns0:v>0</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q72"/>
     </ns0:row>
     <ns0:row r="73" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A73" s="6" t="n">
@@ -8052,12 +7626,8 @@
       <ns0:c r="C73" s="1" t="n">
         <ns0:v>18</ns0:v>
       </ns0:c>
-      <ns0:c r="D73" s="1" t="n">
-        <ns0:v>435.04</ns0:v>
-      </ns0:c>
-      <ns0:c r="E73" s="1" t="n">
-        <ns0:v>390.38</ns0:v>
-      </ns0:c>
+      <ns0:c r="D73" s="1"/>
+      <ns0:c r="E73" s="1"/>
       <ns0:c r="F73" s="1" t="n">
         <ns0:v>833</ns0:v>
       </ns0:c>
@@ -8091,9 +7661,7 @@
       <ns0:c r="P73" s="1" t="n">
         <ns0:v>65</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q73" t="n">
-        <ns0:v>0</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q73"/>
     </ns0:row>
     <ns0:row r="74" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A74" s="6" t="n">
@@ -8105,12 +7673,8 @@
       <ns0:c r="C74" s="1" t="n">
         <ns0:v>19</ns0:v>
       </ns0:c>
-      <ns0:c r="D74" s="1" t="n">
-        <ns0:v>369.51</ns0:v>
-      </ns0:c>
-      <ns0:c r="E74" s="1" t="n">
-        <ns0:v>385.45</ns0:v>
-      </ns0:c>
+      <ns0:c r="D74" s="1"/>
+      <ns0:c r="E74" s="1"/>
       <ns0:c r="F74" s="1" t="n">
         <ns0:v>833</ns0:v>
       </ns0:c>
@@ -8144,9 +7708,7 @@
       <ns0:c r="P74" s="1" t="n">
         <ns0:v>65</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q74" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q74"/>
     </ns0:row>
     <ns0:row r="75" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A75" s="6" t="n">
@@ -8158,12 +7720,8 @@
       <ns0:c r="C75" s="1" t="n">
         <ns0:v>19</ns0:v>
       </ns0:c>
-      <ns0:c r="D75" s="1" t="n">
-        <ns0:v>369.51</ns0:v>
-      </ns0:c>
-      <ns0:c r="E75" s="1" t="n">
-        <ns0:v>358.07</ns0:v>
-      </ns0:c>
+      <ns0:c r="D75" s="1"/>
+      <ns0:c r="E75" s="1"/>
       <ns0:c r="F75" s="1" t="n">
         <ns0:v>613</ns0:v>
       </ns0:c>
@@ -8197,9 +7755,7 @@
       <ns0:c r="P75" s="1" t="n">
         <ns0:v>65</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q75" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q75"/>
     </ns0:row>
     <ns0:row r="76" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A76" s="6" t="n">
@@ -8211,12 +7767,8 @@
       <ns0:c r="C76" s="1" t="n">
         <ns0:v>19</ns0:v>
       </ns0:c>
-      <ns0:c r="D76" s="1" t="n">
-        <ns0:v>369.51</ns0:v>
-      </ns0:c>
-      <ns0:c r="E76" s="1" t="n">
-        <ns0:v>355.73</ns0:v>
-      </ns0:c>
+      <ns0:c r="D76" s="1"/>
+      <ns0:c r="E76" s="1"/>
       <ns0:c r="F76" s="1" t="n">
         <ns0:v>453</ns0:v>
       </ns0:c>
@@ -8250,9 +7802,7 @@
       <ns0:c r="P76" s="1" t="n">
         <ns0:v>65</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q76" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q76"/>
     </ns0:row>
     <ns0:row r="77" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A77" s="6" t="n">
@@ -8264,12 +7814,8 @@
       <ns0:c r="C77" s="1" t="n">
         <ns0:v>19</ns0:v>
       </ns0:c>
-      <ns0:c r="D77" s="1" t="n">
-        <ns0:v>369.51</ns0:v>
-      </ns0:c>
-      <ns0:c r="E77" s="1" t="n">
-        <ns0:v>345</ns0:v>
-      </ns0:c>
+      <ns0:c r="D77" s="1"/>
+      <ns0:c r="E77" s="1"/>
       <ns0:c r="F77" s="1" t="n">
         <ns0:v>368</ns0:v>
       </ns0:c>
@@ -8303,9 +7849,7 @@
       <ns0:c r="P77" s="1" t="n">
         <ns0:v>65</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q77" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q77"/>
     </ns0:row>
     <ns0:row r="78" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A78" s="6" t="n">
@@ -8317,12 +7861,8 @@
       <ns0:c r="C78" s="1" t="n">
         <ns0:v>20</ns0:v>
       </ns0:c>
-      <ns0:c r="D78" s="1" t="n">
-        <ns0:v>195</ns0:v>
-      </ns0:c>
-      <ns0:c r="E78" s="1" t="n">
-        <ns0:v>330.79</ns0:v>
-      </ns0:c>
+      <ns0:c r="D78" s="1"/>
+      <ns0:c r="E78" s="1"/>
       <ns0:c r="F78" s="1" t="n">
         <ns0:v>288</ns0:v>
       </ns0:c>
@@ -8356,9 +7896,7 @@
       <ns0:c r="P78" s="1" t="n">
         <ns0:v>65</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q78" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q78"/>
     </ns0:row>
     <ns0:row r="79" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A79" s="6" t="n">
@@ -8370,12 +7908,8 @@
       <ns0:c r="C79" s="1" t="n">
         <ns0:v>20</ns0:v>
       </ns0:c>
-      <ns0:c r="D79" s="1" t="n">
-        <ns0:v>195</ns0:v>
-      </ns0:c>
-      <ns0:c r="E79" s="1" t="n">
-        <ns0:v>275.26</ns0:v>
-      </ns0:c>
+      <ns0:c r="D79" s="1"/>
+      <ns0:c r="E79" s="1"/>
       <ns0:c r="F79" s="1" t="n">
         <ns0:v>198</ns0:v>
       </ns0:c>
@@ -8409,9 +7943,7 @@
       <ns0:c r="P79" s="1" t="n">
         <ns0:v>65</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q79" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q79"/>
     </ns0:row>
     <ns0:row r="80" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A80" s="6" t="n">
@@ -8423,12 +7955,8 @@
       <ns0:c r="C80" s="1" t="n">
         <ns0:v>20</ns0:v>
       </ns0:c>
-      <ns0:c r="D80" s="1" t="n">
-        <ns0:v>195</ns0:v>
-      </ns0:c>
-      <ns0:c r="E80" s="1" t="n">
-        <ns0:v>282.13</ns0:v>
-      </ns0:c>
+      <ns0:c r="D80" s="1"/>
+      <ns0:c r="E80" s="1"/>
       <ns0:c r="F80" s="1" t="n">
         <ns0:v>65</ns0:v>
       </ns0:c>
@@ -8462,9 +7990,7 @@
       <ns0:c r="P80" s="1" t="n">
         <ns0:v>65</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q80" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q80"/>
     </ns0:row>
     <ns0:row r="81" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A81" s="6" t="n">
@@ -8476,12 +8002,8 @@
       <ns0:c r="C81" s="1" t="n">
         <ns0:v>20</ns0:v>
       </ns0:c>
-      <ns0:c r="D81" s="1" t="n">
-        <ns0:v>195</ns0:v>
-      </ns0:c>
-      <ns0:c r="E81" s="1" t="n">
-        <ns0:v>328.38</ns0:v>
-      </ns0:c>
+      <ns0:c r="D81" s="1"/>
+      <ns0:c r="E81" s="1"/>
       <ns0:c r="F81" s="1" t="n">
         <ns0:v>62</ns0:v>
       </ns0:c>
@@ -8515,9 +8037,7 @@
       <ns0:c r="P81" s="1" t="n">
         <ns0:v>65</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q81" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q81"/>
     </ns0:row>
     <ns0:row r="82" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A82" s="6" t="n">
@@ -8529,12 +8049,8 @@
       <ns0:c r="C82" s="1" t="n">
         <ns0:v>21</ns0:v>
       </ns0:c>
-      <ns0:c r="D82" s="1" t="n">
-        <ns0:v>167.11</ns0:v>
-      </ns0:c>
-      <ns0:c r="E82" s="1" t="n">
-        <ns0:v>328.38</ns0:v>
-      </ns0:c>
+      <ns0:c r="D82" s="1"/>
+      <ns0:c r="E82" s="1"/>
       <ns0:c r="F82" s="1" t="n">
         <ns0:v>48</ns0:v>
       </ns0:c>
@@ -8568,9 +8084,7 @@
       <ns0:c r="P82" s="1" t="n">
         <ns0:v>65</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q82" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q82"/>
     </ns0:row>
     <ns0:row r="83" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A83" s="6" t="n">
@@ -8582,12 +8096,8 @@
       <ns0:c r="C83" s="1" t="n">
         <ns0:v>21</ns0:v>
       </ns0:c>
-      <ns0:c r="D83" s="1" t="n">
-        <ns0:v>167.11</ns0:v>
-      </ns0:c>
-      <ns0:c r="E83" s="1" t="n">
-        <ns0:v>353.54</ns0:v>
-      </ns0:c>
+      <ns0:c r="D83" s="1"/>
+      <ns0:c r="E83" s="1"/>
       <ns0:c r="F83" s="1" t="n">
         <ns0:v>48</ns0:v>
       </ns0:c>
@@ -8621,9 +8131,7 @@
       <ns0:c r="P83" s="1" t="n">
         <ns0:v>65</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q83" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q83"/>
     </ns0:row>
     <ns0:row r="84" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A84" s="6" t="n">
@@ -8635,12 +8143,8 @@
       <ns0:c r="C84" s="1" t="n">
         <ns0:v>21</ns0:v>
       </ns0:c>
-      <ns0:c r="D84" s="1" t="n">
-        <ns0:v>167.11</ns0:v>
-      </ns0:c>
-      <ns0:c r="E84" s="1" t="n">
-        <ns0:v>354.69</ns0:v>
-      </ns0:c>
+      <ns0:c r="D84" s="1"/>
+      <ns0:c r="E84" s="1"/>
       <ns0:c r="F84" s="1" t="n">
         <ns0:v>32</ns0:v>
       </ns0:c>
@@ -8674,9 +8178,7 @@
       <ns0:c r="P84" s="1" t="n">
         <ns0:v>65</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q84" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q84"/>
     </ns0:row>
     <ns0:row r="85" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A85" s="6" t="n">
@@ -8688,12 +8190,8 @@
       <ns0:c r="C85" s="1" t="n">
         <ns0:v>21</ns0:v>
       </ns0:c>
-      <ns0:c r="D85" s="1" t="n">
-        <ns0:v>167.11</ns0:v>
-      </ns0:c>
-      <ns0:c r="E85" s="1" t="n">
-        <ns0:v>358.07</ns0:v>
-      </ns0:c>
+      <ns0:c r="D85" s="1"/>
+      <ns0:c r="E85" s="1"/>
       <ns0:c r="F85" s="1" t="n">
         <ns0:v>16</ns0:v>
       </ns0:c>
@@ -8727,9 +8225,7 @@
       <ns0:c r="P85" s="1" t="n">
         <ns0:v>65</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q85" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q85"/>
     </ns0:row>
     <ns0:row r="86" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A86" s="6" t="n">
@@ -8741,12 +8237,8 @@
       <ns0:c r="C86" s="1" t="n">
         <ns0:v>22</ns0:v>
       </ns0:c>
-      <ns0:c r="D86" s="1" t="n">
-        <ns0:v>270</ns0:v>
-      </ns0:c>
-      <ns0:c r="E86" s="1" t="n">
-        <ns0:v>390.54</ns0:v>
-      </ns0:c>
+      <ns0:c r="D86" s="1"/>
+      <ns0:c r="E86" s="1"/>
       <ns0:c r="F86" s="1" t="n">
         <ns0:v>0</ns0:v>
       </ns0:c>
@@ -8780,9 +8272,7 @@
       <ns0:c r="P86" s="1" t="n">
         <ns0:v>65</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q86" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q86"/>
     </ns0:row>
     <ns0:row r="87" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A87" s="6" t="n">
@@ -8794,12 +8284,8 @@
       <ns0:c r="C87" s="1" t="n">
         <ns0:v>22</ns0:v>
       </ns0:c>
-      <ns0:c r="D87" s="1" t="n">
-        <ns0:v>270</ns0:v>
-      </ns0:c>
-      <ns0:c r="E87" s="1" t="n">
-        <ns0:v>362.98</ns0:v>
-      </ns0:c>
+      <ns0:c r="D87" s="1"/>
+      <ns0:c r="E87" s="1"/>
       <ns0:c r="F87" s="1" t="n">
         <ns0:v>0</ns0:v>
       </ns0:c>
@@ -8833,9 +8319,7 @@
       <ns0:c r="P87" s="1" t="n">
         <ns0:v>65</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q87" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q87"/>
     </ns0:row>
     <ns0:row r="88" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A88" s="6" t="n">
@@ -8847,12 +8331,8 @@
       <ns0:c r="C88" s="1" t="n">
         <ns0:v>22</ns0:v>
       </ns0:c>
-      <ns0:c r="D88" s="1" t="n">
-        <ns0:v>270</ns0:v>
-      </ns0:c>
-      <ns0:c r="E88" s="1" t="n">
-        <ns0:v>353</ns0:v>
-      </ns0:c>
+      <ns0:c r="D88" s="1"/>
+      <ns0:c r="E88" s="1"/>
       <ns0:c r="F88" s="1" t="n">
         <ns0:v>0</ns0:v>
       </ns0:c>
@@ -8886,9 +8366,7 @@
       <ns0:c r="P88" s="1" t="n">
         <ns0:v>65</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q88" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q88"/>
     </ns0:row>
     <ns0:row r="89" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A89" s="6" t="n">
@@ -8900,12 +8378,8 @@
       <ns0:c r="C89" s="1" t="n">
         <ns0:v>22</ns0:v>
       </ns0:c>
-      <ns0:c r="D89" s="1" t="n">
-        <ns0:v>270</ns0:v>
-      </ns0:c>
-      <ns0:c r="E89" s="1" t="n">
-        <ns0:v>310</ns0:v>
-      </ns0:c>
+      <ns0:c r="D89" s="1"/>
+      <ns0:c r="E89" s="1"/>
       <ns0:c r="F89" s="1" t="n">
         <ns0:v>0</ns0:v>
       </ns0:c>
@@ -8939,9 +8413,7 @@
       <ns0:c r="P89" s="1" t="n">
         <ns0:v>65</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q89" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q89"/>
     </ns0:row>
     <ns0:row r="90" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A90" s="6" t="n">
@@ -8953,12 +8425,8 @@
       <ns0:c r="C90" s="1" t="n">
         <ns0:v>23</ns0:v>
       </ns0:c>
-      <ns0:c r="D90" s="1" t="n">
-        <ns0:v>234.16</ns0:v>
-      </ns0:c>
-      <ns0:c r="E90" s="1" t="n">
-        <ns0:v>279.92</ns0:v>
-      </ns0:c>
+      <ns0:c r="D90" s="1"/>
+      <ns0:c r="E90" s="1"/>
       <ns0:c r="F90" s="1" t="n">
         <ns0:v>35</ns0:v>
       </ns0:c>
@@ -8992,9 +8460,7 @@
       <ns0:c r="P90" s="1" t="n">
         <ns0:v>65</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q90" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q90"/>
     </ns0:row>
     <ns0:row r="91" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A91" s="6" t="n">
@@ -9006,12 +8472,8 @@
       <ns0:c r="C91" s="1" t="n">
         <ns0:v>23</ns0:v>
       </ns0:c>
-      <ns0:c r="D91" s="1" t="n">
-        <ns0:v>234.16</ns0:v>
-      </ns0:c>
-      <ns0:c r="E91" s="1" t="n">
-        <ns0:v>350.29</ns0:v>
-      </ns0:c>
+      <ns0:c r="D91" s="1"/>
+      <ns0:c r="E91" s="1"/>
       <ns0:c r="F91" s="1" t="n">
         <ns0:v>35</ns0:v>
       </ns0:c>
@@ -9045,9 +8507,7 @@
       <ns0:c r="P91" s="1" t="n">
         <ns0:v>65</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q91" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q91"/>
     </ns0:row>
     <ns0:row r="92" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A92" s="6" t="n">
@@ -9059,12 +8519,8 @@
       <ns0:c r="C92" s="1" t="n">
         <ns0:v>23</ns0:v>
       </ns0:c>
-      <ns0:c r="D92" s="1" t="n">
-        <ns0:v>234.16</ns0:v>
-      </ns0:c>
-      <ns0:c r="E92" s="1" t="n">
-        <ns0:v>335.98</ns0:v>
-      </ns0:c>
+      <ns0:c r="D92" s="1"/>
+      <ns0:c r="E92" s="1"/>
       <ns0:c r="F92" s="1" t="n">
         <ns0:v>35</ns0:v>
       </ns0:c>
@@ -9098,9 +8554,7 @@
       <ns0:c r="P92" s="1" t="n">
         <ns0:v>65</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q92" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q92"/>
     </ns0:row>
     <ns0:row r="93" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A93" s="6" t="n">
@@ -9112,12 +8566,8 @@
       <ns0:c r="C93" s="1" t="n">
         <ns0:v>23</ns0:v>
       </ns0:c>
-      <ns0:c r="D93" s="1" t="n">
-        <ns0:v>234.16</ns0:v>
-      </ns0:c>
-      <ns0:c r="E93" s="1" t="n">
-        <ns0:v>282.1</ns0:v>
-      </ns0:c>
+      <ns0:c r="D93" s="1"/>
+      <ns0:c r="E93" s="1"/>
       <ns0:c r="F93" s="1" t="n">
         <ns0:v>35</ns0:v>
       </ns0:c>
@@ -9151,9 +8601,7 @@
       <ns0:c r="P93" s="1" t="n">
         <ns0:v>65</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q93" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q93"/>
     </ns0:row>
     <ns0:row r="94" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A94" s="6" t="n">
@@ -9165,12 +8613,8 @@
       <ns0:c r="C94" s="1" t="n">
         <ns0:v>24</ns0:v>
       </ns0:c>
-      <ns0:c r="D94" s="1" t="n">
-        <ns0:v>155.86</ns0:v>
-      </ns0:c>
-      <ns0:c r="E94" s="1" t="n">
-        <ns0:v>310</ns0:v>
-      </ns0:c>
+      <ns0:c r="D94" s="1"/>
+      <ns0:c r="E94" s="1"/>
       <ns0:c r="F94" s="1" t="n">
         <ns0:v>35</ns0:v>
       </ns0:c>
@@ -9204,9 +8648,7 @@
       <ns0:c r="P94" s="1" t="n">
         <ns0:v>65</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q94" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q94"/>
     </ns0:row>
     <ns0:row r="95" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A95" s="6" t="n">
@@ -9218,12 +8660,8 @@
       <ns0:c r="C95" s="1" t="n">
         <ns0:v>24</ns0:v>
       </ns0:c>
-      <ns0:c r="D95" s="1" t="n">
-        <ns0:v>155.86</ns0:v>
-      </ns0:c>
-      <ns0:c r="E95" s="1" t="n">
-        <ns0:v>287.55</ns0:v>
-      </ns0:c>
+      <ns0:c r="D95" s="1"/>
+      <ns0:c r="E95" s="1"/>
       <ns0:c r="F95" s="1" t="n">
         <ns0:v>35</ns0:v>
       </ns0:c>
@@ -9257,9 +8695,7 @@
       <ns0:c r="P95" s="1" t="n">
         <ns0:v>65</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q95" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q95"/>
     </ns0:row>
     <ns0:row r="96" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A96" s="6" t="n">
@@ -9271,12 +8707,8 @@
       <ns0:c r="C96" s="1" t="n">
         <ns0:v>24</ns0:v>
       </ns0:c>
-      <ns0:c r="D96" s="1" t="n">
-        <ns0:v>155.86</ns0:v>
-      </ns0:c>
-      <ns0:c r="E96" s="1" t="n">
-        <ns0:v>276.08</ns0:v>
-      </ns0:c>
+      <ns0:c r="D96" s="1"/>
+      <ns0:c r="E96" s="1"/>
       <ns0:c r="F96" s="1" t="n">
         <ns0:v>35</ns0:v>
       </ns0:c>
@@ -9310,9 +8742,7 @@
       <ns0:c r="P96" s="1" t="n">
         <ns0:v>65</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q96" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q96"/>
     </ns0:row>
     <ns0:row r="97" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A97" s="6" t="n">
@@ -9326,12 +8756,8 @@
       <ns0:c r="C97" s="1" t="n">
         <ns0:v>24</ns0:v>
       </ns0:c>
-      <ns0:c r="D97" s="1" t="n">
-        <ns0:v>155.86</ns0:v>
-      </ns0:c>
-      <ns0:c r="E97" s="1" t="n">
-        <ns0:v>279.44</ns0:v>
-      </ns0:c>
+      <ns0:c r="D97" s="1"/>
+      <ns0:c r="E97" s="1"/>
       <ns0:c r="F97" s="1" t="n">
         <ns0:v>35</ns0:v>
       </ns0:c>
@@ -9365,9 +8791,7 @@
       <ns0:c r="P97" s="1" t="n">
         <ns0:v>65</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q97" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q97"/>
     </ns0:row>
   </ns0:sheetData>
   <conditionalFormatting sqref="A1:B1">

--- a/review-results/河北实时运行及市场出清数据-20261016.xlsx
+++ b/review-results/河北实时运行及市场出清数据-20261016.xlsx
@@ -4289,8 +4289,12 @@
       <ns0:c r="C2" s="1" t="n">
         <ns0:v>1</ns0:v>
       </ns0:c>
-      <ns0:c r="D2" s="1"/>
-      <ns0:c r="E2" s="1"/>
+      <ns0:c r="D2" s="1" t="n">
+        <ns0:v>355.48</ns0:v>
+      </ns0:c>
+      <ns0:c r="E2" s="1" t="n">
+        <ns0:v>433.51</ns0:v>
+      </ns0:c>
       <ns0:c r="F2" s="1" t="n">
         <ns0:v>33</ns0:v>
       </ns0:c>
@@ -4324,7 +4328,9 @@
       <ns0:c r="P2" s="1" t="n">
         <ns0:v>62</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q2"/>
+      <ns0:c s="1" r="Q2" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="3" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A3" s="6" t="n">
@@ -4336,8 +4342,12 @@
       <ns0:c r="C3" s="1" t="n">
         <ns0:v>1</ns0:v>
       </ns0:c>
-      <ns0:c r="D3" s="1"/>
-      <ns0:c r="E3" s="1"/>
+      <ns0:c r="D3" s="1" t="n">
+        <ns0:v>355.48</ns0:v>
+      </ns0:c>
+      <ns0:c r="E3" s="1" t="n">
+        <ns0:v>474.79</ns0:v>
+      </ns0:c>
       <ns0:c r="F3" s="1" t="n">
         <ns0:v>33</ns0:v>
       </ns0:c>
@@ -4371,7 +4381,9 @@
       <ns0:c r="P3" s="1" t="n">
         <ns0:v>62</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q3"/>
+      <ns0:c s="1" r="Q3" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="4" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A4" s="6" t="n">
@@ -4383,8 +4395,12 @@
       <ns0:c r="C4" s="1" t="n">
         <ns0:v>1</ns0:v>
       </ns0:c>
-      <ns0:c r="D4" s="1"/>
-      <ns0:c r="E4" s="1"/>
+      <ns0:c r="D4" s="1" t="n">
+        <ns0:v>355.48</ns0:v>
+      </ns0:c>
+      <ns0:c r="E4" s="1" t="n">
+        <ns0:v>465</ns0:v>
+      </ns0:c>
       <ns0:c r="F4" s="1" t="n">
         <ns0:v>33</ns0:v>
       </ns0:c>
@@ -4418,7 +4434,9 @@
       <ns0:c r="P4" s="1" t="n">
         <ns0:v>63</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q4"/>
+      <ns0:c s="1" r="Q4" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="5" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A5" s="6" t="n">
@@ -4430,8 +4448,12 @@
       <ns0:c r="C5" s="1" t="n">
         <ns0:v>1</ns0:v>
       </ns0:c>
-      <ns0:c r="D5" s="1"/>
-      <ns0:c r="E5" s="1"/>
+      <ns0:c r="D5" s="1" t="n">
+        <ns0:v>355.48</ns0:v>
+      </ns0:c>
+      <ns0:c r="E5" s="1" t="n">
+        <ns0:v>464.8</ns0:v>
+      </ns0:c>
       <ns0:c r="F5" s="1" t="n">
         <ns0:v>33</ns0:v>
       </ns0:c>
@@ -4465,7 +4487,9 @@
       <ns0:c r="P5" s="1" t="n">
         <ns0:v>63</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q5"/>
+      <ns0:c s="1" r="Q5" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="6" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A6" s="6" t="n">
@@ -4477,8 +4501,12 @@
       <ns0:c r="C6" s="1" t="n">
         <ns0:v>2</ns0:v>
       </ns0:c>
-      <ns0:c r="D6" s="1"/>
-      <ns0:c r="E6" s="1"/>
+      <ns0:c r="D6" s="1" t="n">
+        <ns0:v>369.51</ns0:v>
+      </ns0:c>
+      <ns0:c r="E6" s="1" t="n">
+        <ns0:v>445</ns0:v>
+      </ns0:c>
       <ns0:c r="F6" s="1" t="n">
         <ns0:v>33</ns0:v>
       </ns0:c>
@@ -4512,7 +4540,9 @@
       <ns0:c r="P6" s="1" t="n">
         <ns0:v>63</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q6"/>
+      <ns0:c s="1" r="Q6" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="7" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A7" s="6" t="n">
@@ -4524,8 +4554,12 @@
       <ns0:c r="C7" s="1" t="n">
         <ns0:v>2</ns0:v>
       </ns0:c>
-      <ns0:c r="D7" s="1"/>
-      <ns0:c r="E7" s="1"/>
+      <ns0:c r="D7" s="1" t="n">
+        <ns0:v>369.51</ns0:v>
+      </ns0:c>
+      <ns0:c r="E7" s="1" t="n">
+        <ns0:v>441.51</ns0:v>
+      </ns0:c>
       <ns0:c r="F7" s="1" t="n">
         <ns0:v>33</ns0:v>
       </ns0:c>
@@ -4559,7 +4593,9 @@
       <ns0:c r="P7" s="1" t="n">
         <ns0:v>63</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q7"/>
+      <ns0:c s="1" r="Q7" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="8" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A8" s="6" t="n">
@@ -4571,8 +4607,12 @@
       <ns0:c r="C8" s="1" t="n">
         <ns0:v>2</ns0:v>
       </ns0:c>
-      <ns0:c r="D8" s="1"/>
-      <ns0:c r="E8" s="1"/>
+      <ns0:c r="D8" s="1" t="n">
+        <ns0:v>369.51</ns0:v>
+      </ns0:c>
+      <ns0:c r="E8" s="1" t="n">
+        <ns0:v>430.36</ns0:v>
+      </ns0:c>
       <ns0:c r="F8" s="1" t="n">
         <ns0:v>33</ns0:v>
       </ns0:c>
@@ -4606,7 +4646,9 @@
       <ns0:c r="P8" s="1" t="n">
         <ns0:v>64</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q8"/>
+      <ns0:c s="1" r="Q8" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="9" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A9" s="6" t="n">
@@ -4618,8 +4660,12 @@
       <ns0:c r="C9" s="1" t="n">
         <ns0:v>2</ns0:v>
       </ns0:c>
-      <ns0:c r="D9" s="1"/>
-      <ns0:c r="E9" s="1"/>
+      <ns0:c r="D9" s="1" t="n">
+        <ns0:v>369.35</ns0:v>
+      </ns0:c>
+      <ns0:c r="E9" s="1" t="n">
+        <ns0:v>431.57</ns0:v>
+      </ns0:c>
       <ns0:c r="F9" s="1" t="n">
         <ns0:v>33</ns0:v>
       </ns0:c>
@@ -4653,7 +4699,9 @@
       <ns0:c r="P9" s="1" t="n">
         <ns0:v>64</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q9"/>
+      <ns0:c s="1" r="Q9" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="10" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A10" s="6" t="n">
@@ -4665,8 +4713,12 @@
       <ns0:c r="C10" s="1" t="n">
         <ns0:v>3</ns0:v>
       </ns0:c>
-      <ns0:c r="D10" s="1"/>
-      <ns0:c r="E10" s="1"/>
+      <ns0:c r="D10" s="1" t="n">
+        <ns0:v>390.54</ns0:v>
+      </ns0:c>
+      <ns0:c r="E10" s="1" t="n">
+        <ns0:v>474.23</ns0:v>
+      </ns0:c>
       <ns0:c r="F10" s="1" t="n">
         <ns0:v>133</ns0:v>
       </ns0:c>
@@ -4700,7 +4752,9 @@
       <ns0:c r="P10" s="1" t="n">
         <ns0:v>64</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q10"/>
+      <ns0:c s="1" r="Q10" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="11" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A11" s="6" t="n">
@@ -4712,8 +4766,12 @@
       <ns0:c r="C11" s="1" t="n">
         <ns0:v>3</ns0:v>
       </ns0:c>
-      <ns0:c r="D11" s="1"/>
-      <ns0:c r="E11" s="1"/>
+      <ns0:c r="D11" s="1" t="n">
+        <ns0:v>390.54</ns0:v>
+      </ns0:c>
+      <ns0:c r="E11" s="1" t="n">
+        <ns0:v>465</ns0:v>
+      </ns0:c>
       <ns0:c r="F11" s="1" t="n">
         <ns0:v>133</ns0:v>
       </ns0:c>
@@ -4747,7 +4805,9 @@
       <ns0:c r="P11" s="1" t="n">
         <ns0:v>64</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q11"/>
+      <ns0:c s="1" r="Q11" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="12" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A12" s="6" t="n">
@@ -4759,8 +4819,12 @@
       <ns0:c r="C12" s="1" t="n">
         <ns0:v>3</ns0:v>
       </ns0:c>
-      <ns0:c r="D12" s="1"/>
-      <ns0:c r="E12" s="1"/>
+      <ns0:c r="D12" s="1" t="n">
+        <ns0:v>390.54</ns0:v>
+      </ns0:c>
+      <ns0:c r="E12" s="1" t="n">
+        <ns0:v>433.73</ns0:v>
+      </ns0:c>
       <ns0:c r="F12" s="1" t="n">
         <ns0:v>133</ns0:v>
       </ns0:c>
@@ -4794,7 +4858,9 @@
       <ns0:c r="P12" s="1" t="n">
         <ns0:v>64</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q12"/>
+      <ns0:c s="1" r="Q12" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="13" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A13" s="6" t="n">
@@ -4806,8 +4872,12 @@
       <ns0:c r="C13" s="1" t="n">
         <ns0:v>3</ns0:v>
       </ns0:c>
-      <ns0:c r="D13" s="1"/>
-      <ns0:c r="E13" s="1"/>
+      <ns0:c r="D13" s="1" t="n">
+        <ns0:v>390.54</ns0:v>
+      </ns0:c>
+      <ns0:c r="E13" s="1" t="n">
+        <ns0:v>429.32</ns0:v>
+      </ns0:c>
       <ns0:c r="F13" s="1" t="n">
         <ns0:v>0</ns0:v>
       </ns0:c>
@@ -4841,7 +4911,9 @@
       <ns0:c r="P13" s="1" t="n">
         <ns0:v>64</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q13"/>
+      <ns0:c s="1" r="Q13" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="14" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A14" s="6" t="n">
@@ -4853,8 +4925,12 @@
       <ns0:c r="C14" s="1" t="n">
         <ns0:v>4</ns0:v>
       </ns0:c>
-      <ns0:c r="D14" s="1"/>
-      <ns0:c r="E14" s="1"/>
+      <ns0:c r="D14" s="1" t="n">
+        <ns0:v>420</ns0:v>
+      </ns0:c>
+      <ns0:c r="E14" s="1" t="n">
+        <ns0:v>415.25</ns0:v>
+      </ns0:c>
       <ns0:c r="F14" s="1" t="n">
         <ns0:v>0</ns0:v>
       </ns0:c>
@@ -4888,7 +4964,9 @@
       <ns0:c r="P14" s="1" t="n">
         <ns0:v>64</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q14"/>
+      <ns0:c s="1" r="Q14" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="15" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A15" s="6" t="n">
@@ -4900,8 +4978,12 @@
       <ns0:c r="C15" s="1" t="n">
         <ns0:v>4</ns0:v>
       </ns0:c>
-      <ns0:c r="D15" s="1"/>
-      <ns0:c r="E15" s="1"/>
+      <ns0:c r="D15" s="1" t="n">
+        <ns0:v>420</ns0:v>
+      </ns0:c>
+      <ns0:c r="E15" s="1" t="n">
+        <ns0:v>413.35</ns0:v>
+      </ns0:c>
       <ns0:c r="F15" s="1" t="n">
         <ns0:v>0</ns0:v>
       </ns0:c>
@@ -4935,7 +5017,9 @@
       <ns0:c r="P15" s="1" t="n">
         <ns0:v>64</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q15"/>
+      <ns0:c s="1" r="Q15" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="16" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A16" s="6" t="n">
@@ -4947,8 +5031,12 @@
       <ns0:c r="C16" s="1" t="n">
         <ns0:v>4</ns0:v>
       </ns0:c>
-      <ns0:c r="D16" s="1"/>
-      <ns0:c r="E16" s="1"/>
+      <ns0:c r="D16" s="1" t="n">
+        <ns0:v>420</ns0:v>
+      </ns0:c>
+      <ns0:c r="E16" s="1" t="n">
+        <ns0:v>410.67</ns0:v>
+      </ns0:c>
       <ns0:c r="F16" s="1" t="n">
         <ns0:v>0</ns0:v>
       </ns0:c>
@@ -4982,7 +5070,9 @@
       <ns0:c r="P16" s="1" t="n">
         <ns0:v>64</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q16"/>
+      <ns0:c s="1" r="Q16" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="17" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A17" s="6" t="n">
@@ -4994,8 +5084,12 @@
       <ns0:c r="C17" s="1" t="n">
         <ns0:v>4</ns0:v>
       </ns0:c>
-      <ns0:c r="D17" s="1"/>
-      <ns0:c r="E17" s="1"/>
+      <ns0:c r="D17" s="1" t="n">
+        <ns0:v>420</ns0:v>
+      </ns0:c>
+      <ns0:c r="E17" s="1" t="n">
+        <ns0:v>415.25</ns0:v>
+      </ns0:c>
       <ns0:c r="F17" s="1" t="n">
         <ns0:v>0</ns0:v>
       </ns0:c>
@@ -5029,7 +5123,9 @@
       <ns0:c r="P17" s="1" t="n">
         <ns0:v>64</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q17"/>
+      <ns0:c s="1" r="Q17" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="18" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A18" s="6" t="n">
@@ -5041,8 +5137,12 @@
       <ns0:c r="C18" s="1" t="n">
         <ns0:v>5</ns0:v>
       </ns0:c>
-      <ns0:c r="D18" s="1"/>
-      <ns0:c r="E18" s="1"/>
+      <ns0:c r="D18" s="1" t="n">
+        <ns0:v>434.47</ns0:v>
+      </ns0:c>
+      <ns0:c r="E18" s="1" t="n">
+        <ns0:v>410.89</ns0:v>
+      </ns0:c>
       <ns0:c r="F18" s="1" t="n">
         <ns0:v>180</ns0:v>
       </ns0:c>
@@ -5076,7 +5176,9 @@
       <ns0:c r="P18" s="1" t="n">
         <ns0:v>64</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q18"/>
+      <ns0:c s="1" r="Q18" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="19" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A19" s="6" t="n">
@@ -5088,8 +5190,12 @@
       <ns0:c r="C19" s="1" t="n">
         <ns0:v>5</ns0:v>
       </ns0:c>
-      <ns0:c r="D19" s="1"/>
-      <ns0:c r="E19" s="1"/>
+      <ns0:c r="D19" s="1" t="n">
+        <ns0:v>434.47</ns0:v>
+      </ns0:c>
+      <ns0:c r="E19" s="1" t="n">
+        <ns0:v>411.83</ns0:v>
+      </ns0:c>
       <ns0:c r="F19" s="1" t="n">
         <ns0:v>300</ns0:v>
       </ns0:c>
@@ -5123,7 +5229,9 @@
       <ns0:c r="P19" s="1" t="n">
         <ns0:v>64</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q19"/>
+      <ns0:c s="1" r="Q19" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="20" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A20" s="6" t="n">
@@ -5135,8 +5243,12 @@
       <ns0:c r="C20" s="1" t="n">
         <ns0:v>5</ns0:v>
       </ns0:c>
-      <ns0:c r="D20" s="1"/>
-      <ns0:c r="E20" s="1"/>
+      <ns0:c r="D20" s="1" t="n">
+        <ns0:v>434.47</ns0:v>
+      </ns0:c>
+      <ns0:c r="E20" s="1" t="n">
+        <ns0:v>410</ns0:v>
+      </ns0:c>
       <ns0:c r="F20" s="1" t="n">
         <ns0:v>640</ns0:v>
       </ns0:c>
@@ -5170,7 +5282,9 @@
       <ns0:c r="P20" s="1" t="n">
         <ns0:v>64</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q20"/>
+      <ns0:c s="1" r="Q20" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="21" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A21" s="6" t="n">
@@ -5182,8 +5296,12 @@
       <ns0:c r="C21" s="1" t="n">
         <ns0:v>5</ns0:v>
       </ns0:c>
-      <ns0:c r="D21" s="1"/>
-      <ns0:c r="E21" s="1"/>
+      <ns0:c r="D21" s="1" t="n">
+        <ns0:v>434.47</ns0:v>
+      </ns0:c>
+      <ns0:c r="E21" s="1" t="n">
+        <ns0:v>390.38</ns0:v>
+      </ns0:c>
       <ns0:c r="F21" s="1" t="n">
         <ns0:v>780</ns0:v>
       </ns0:c>
@@ -5217,7 +5335,9 @@
       <ns0:c r="P21" s="1" t="n">
         <ns0:v>64</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q21"/>
+      <ns0:c s="1" r="Q21" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="22" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A22" s="6" t="n">
@@ -5229,8 +5349,12 @@
       <ns0:c r="C22" s="1" t="n">
         <ns0:v>6</ns0:v>
       </ns0:c>
-      <ns0:c r="D22" s="1"/>
-      <ns0:c r="E22" s="1"/>
+      <ns0:c r="D22" s="1" t="n">
+        <ns0:v>446.76</ns0:v>
+      </ns0:c>
+      <ns0:c r="E22" s="1" t="n">
+        <ns0:v>370</ns0:v>
+      </ns0:c>
       <ns0:c r="F22" s="1" t="n">
         <ns0:v>1320</ns0:v>
       </ns0:c>
@@ -5264,7 +5388,9 @@
       <ns0:c r="P22" s="1" t="n">
         <ns0:v>64</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q22"/>
+      <ns0:c s="1" r="Q22" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="23" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A23" s="6" t="n">
@@ -5276,8 +5402,12 @@
       <ns0:c r="C23" s="1" t="n">
         <ns0:v>6</ns0:v>
       </ns0:c>
-      <ns0:c r="D23" s="1"/>
-      <ns0:c r="E23" s="1"/>
+      <ns0:c r="D23" s="1" t="n">
+        <ns0:v>446.76</ns0:v>
+      </ns0:c>
+      <ns0:c r="E23" s="1" t="n">
+        <ns0:v>358.07</ns0:v>
+      </ns0:c>
       <ns0:c r="F23" s="1" t="n">
         <ns0:v>1810</ns0:v>
       </ns0:c>
@@ -5311,7 +5441,9 @@
       <ns0:c r="P23" s="1" t="n">
         <ns0:v>64</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q23"/>
+      <ns0:c s="1" r="Q23" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="24" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A24" s="6" t="n">
@@ -5323,8 +5455,12 @@
       <ns0:c r="C24" s="1" t="n">
         <ns0:v>6</ns0:v>
       </ns0:c>
-      <ns0:c r="D24" s="1"/>
-      <ns0:c r="E24" s="1"/>
+      <ns0:c r="D24" s="1" t="n">
+        <ns0:v>446.76</ns0:v>
+      </ns0:c>
+      <ns0:c r="E24" s="1" t="n">
+        <ns0:v>353.54</ns0:v>
+      </ns0:c>
       <ns0:c r="F24" s="1" t="n">
         <ns0:v>2030</ns0:v>
       </ns0:c>
@@ -5358,7 +5494,9 @@
       <ns0:c r="P24" s="1" t="n">
         <ns0:v>64</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q24"/>
+      <ns0:c s="1" r="Q24" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="25" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A25" s="6" t="n">
@@ -5370,8 +5508,12 @@
       <ns0:c r="C25" s="1" t="n">
         <ns0:v>6</ns0:v>
       </ns0:c>
-      <ns0:c r="D25" s="1"/>
-      <ns0:c r="E25" s="1"/>
+      <ns0:c r="D25" s="1" t="n">
+        <ns0:v>446.76</ns0:v>
+      </ns0:c>
+      <ns0:c r="E25" s="1" t="n">
+        <ns0:v>355.48</ns0:v>
+      </ns0:c>
       <ns0:c r="F25" s="1" t="n">
         <ns0:v>2010</ns0:v>
       </ns0:c>
@@ -5405,7 +5547,9 @@
       <ns0:c r="P25" s="1" t="n">
         <ns0:v>64</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q25"/>
+      <ns0:c s="1" r="Q25" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="26" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A26" s="6" t="n">
@@ -5417,8 +5561,12 @@
       <ns0:c r="C26" s="1" t="n">
         <ns0:v>7</ns0:v>
       </ns0:c>
-      <ns0:c r="D26" s="1"/>
-      <ns0:c r="E26" s="1"/>
+      <ns0:c r="D26" s="1" t="n">
+        <ns0:v>470</ns0:v>
+      </ns0:c>
+      <ns0:c r="E26" s="1" t="n">
+        <ns0:v>335.98</ns0:v>
+      </ns0:c>
       <ns0:c r="F26" s="1" t="n">
         <ns0:v>2320</ns0:v>
       </ns0:c>
@@ -5452,7 +5600,9 @@
       <ns0:c r="P26" s="1" t="n">
         <ns0:v>65</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q26"/>
+      <ns0:c s="1" r="Q26" t="n">
+        <ns0:v>0</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="27" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A27" s="6" t="n">
@@ -5464,8 +5614,12 @@
       <ns0:c r="C27" s="1" t="n">
         <ns0:v>7</ns0:v>
       </ns0:c>
-      <ns0:c r="D27" s="1"/>
-      <ns0:c r="E27" s="1"/>
+      <ns0:c r="D27" s="1" t="n">
+        <ns0:v>470</ns0:v>
+      </ns0:c>
+      <ns0:c r="E27" s="1" t="n">
+        <ns0:v>350.91</ns0:v>
+      </ns0:c>
       <ns0:c r="F27" s="1" t="n">
         <ns0:v>2305</ns0:v>
       </ns0:c>
@@ -5499,7 +5653,9 @@
       <ns0:c r="P27" s="1" t="n">
         <ns0:v>65</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q27"/>
+      <ns0:c s="1" r="Q27" t="n">
+        <ns0:v>0</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="28" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A28" s="6" t="n">
@@ -5511,8 +5667,12 @@
       <ns0:c r="C28" s="1" t="n">
         <ns0:v>7</ns0:v>
       </ns0:c>
-      <ns0:c r="D28" s="1"/>
-      <ns0:c r="E28" s="1"/>
+      <ns0:c r="D28" s="1" t="n">
+        <ns0:v>470</ns0:v>
+      </ns0:c>
+      <ns0:c r="E28" s="1" t="n">
+        <ns0:v>414.04</ns0:v>
+      </ns0:c>
       <ns0:c r="F28" s="1" t="n">
         <ns0:v>1975</ns0:v>
       </ns0:c>
@@ -5546,7 +5706,9 @@
       <ns0:c r="P28" s="1" t="n">
         <ns0:v>65</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q28"/>
+      <ns0:c s="1" r="Q28" t="n">
+        <ns0:v>0</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="29" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A29" s="6" t="n">
@@ -5558,8 +5720,12 @@
       <ns0:c r="C29" s="1" t="n">
         <ns0:v>7</ns0:v>
       </ns0:c>
-      <ns0:c r="D29" s="1"/>
-      <ns0:c r="E29" s="1"/>
+      <ns0:c r="D29" s="1" t="n">
+        <ns0:v>470</ns0:v>
+      </ns0:c>
+      <ns0:c r="E29" s="1" t="n">
+        <ns0:v>430.14</ns0:v>
+      </ns0:c>
       <ns0:c r="F29" s="1" t="n">
         <ns0:v>1655</ns0:v>
       </ns0:c>
@@ -5593,7 +5759,9 @@
       <ns0:c r="P29" s="1" t="n">
         <ns0:v>65</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q29"/>
+      <ns0:c s="1" r="Q29" t="n">
+        <ns0:v>0</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="30" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A30" s="6" t="n">
@@ -5605,8 +5773,12 @@
       <ns0:c r="C30" s="1" t="n">
         <ns0:v>8</ns0:v>
       </ns0:c>
-      <ns0:c r="D30" s="1"/>
-      <ns0:c r="E30" s="1"/>
+      <ns0:c r="D30" s="1" t="n">
+        <ns0:v>420</ns0:v>
+      </ns0:c>
+      <ns0:c r="E30" s="1" t="n">
+        <ns0:v>445</ns0:v>
+      </ns0:c>
       <ns0:c r="F30" s="1" t="n">
         <ns0:v>980</ns0:v>
       </ns0:c>
@@ -5640,7 +5812,9 @@
       <ns0:c r="P30" s="1" t="n">
         <ns0:v>65</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q30"/>
+      <ns0:c s="1" r="Q30" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="31" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A31" s="6" t="n">
@@ -5652,8 +5826,12 @@
       <ns0:c r="C31" s="1" t="n">
         <ns0:v>8</ns0:v>
       </ns0:c>
-      <ns0:c r="D31" s="1"/>
-      <ns0:c r="E31" s="1"/>
+      <ns0:c r="D31" s="1" t="n">
+        <ns0:v>420</ns0:v>
+      </ns0:c>
+      <ns0:c r="E31" s="1" t="n">
+        <ns0:v>434.35</ns0:v>
+      </ns0:c>
       <ns0:c r="F31" s="1" t="n">
         <ns0:v>694</ns0:v>
       </ns0:c>
@@ -5687,7 +5865,9 @@
       <ns0:c r="P31" s="1" t="n">
         <ns0:v>65</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q31"/>
+      <ns0:c s="1" r="Q31" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="32" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A32" s="6" t="n">
@@ -5699,8 +5879,12 @@
       <ns0:c r="C32" s="1" t="n">
         <ns0:v>8</ns0:v>
       </ns0:c>
-      <ns0:c r="D32" s="1"/>
-      <ns0:c r="E32" s="1"/>
+      <ns0:c r="D32" s="1" t="n">
+        <ns0:v>420</ns0:v>
+      </ns0:c>
+      <ns0:c r="E32" s="1" t="n">
+        <ns0:v>425.45</ns0:v>
+      </ns0:c>
       <ns0:c r="F32" s="1" t="n">
         <ns0:v>155</ns0:v>
       </ns0:c>
@@ -5734,7 +5918,9 @@
       <ns0:c r="P32" s="1" t="n">
         <ns0:v>65</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q32"/>
+      <ns0:c s="1" r="Q32" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="33" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A33" s="6" t="n">
@@ -5746,8 +5932,12 @@
       <ns0:c r="C33" s="1" t="n">
         <ns0:v>8</ns0:v>
       </ns0:c>
-      <ns0:c r="D33" s="1"/>
-      <ns0:c r="E33" s="1"/>
+      <ns0:c r="D33" s="1" t="n">
+        <ns0:v>420</ns0:v>
+      </ns0:c>
+      <ns0:c r="E33" s="1" t="n">
+        <ns0:v>409.66</ns0:v>
+      </ns0:c>
       <ns0:c r="F33" s="1" t="n">
         <ns0:v>40</ns0:v>
       </ns0:c>
@@ -5781,7 +5971,9 @@
       <ns0:c r="P33" s="1" t="n">
         <ns0:v>65</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q33"/>
+      <ns0:c s="1" r="Q33" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="34" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A34" s="6" t="n">
@@ -5793,8 +5985,12 @@
       <ns0:c r="C34" s="1" t="n">
         <ns0:v>9</ns0:v>
       </ns0:c>
-      <ns0:c r="D34" s="1"/>
-      <ns0:c r="E34" s="1"/>
+      <ns0:c r="D34" s="1" t="n">
+        <ns0:v>415.25</ns0:v>
+      </ns0:c>
+      <ns0:c r="E34" s="1" t="n">
+        <ns0:v>395.97</ns0:v>
+      </ns0:c>
       <ns0:c r="F34" s="1" t="n">
         <ns0:v>0</ns0:v>
       </ns0:c>
@@ -5828,7 +6024,9 @@
       <ns0:c r="P34" s="1" t="n">
         <ns0:v>65</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q34"/>
+      <ns0:c s="1" r="Q34" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="35" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A35" s="6" t="n">
@@ -5840,8 +6038,12 @@
       <ns0:c r="C35" s="1" t="n">
         <ns0:v>9</ns0:v>
       </ns0:c>
-      <ns0:c r="D35" s="1"/>
-      <ns0:c r="E35" s="1"/>
+      <ns0:c r="D35" s="1" t="n">
+        <ns0:v>415.25</ns0:v>
+      </ns0:c>
+      <ns0:c r="E35" s="1" t="n">
+        <ns0:v>353.51</ns0:v>
+      </ns0:c>
       <ns0:c r="F35" s="1" t="n">
         <ns0:v>0</ns0:v>
       </ns0:c>
@@ -5875,7 +6077,9 @@
       <ns0:c r="P35" s="1" t="n">
         <ns0:v>65</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q35"/>
+      <ns0:c s="1" r="Q35" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="36" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A36" s="6" t="n">
@@ -5887,8 +6091,12 @@
       <ns0:c r="C36" s="1" t="n">
         <ns0:v>9</ns0:v>
       </ns0:c>
-      <ns0:c r="D36" s="1"/>
-      <ns0:c r="E36" s="1"/>
+      <ns0:c r="D36" s="1" t="n">
+        <ns0:v>415.25</ns0:v>
+      </ns0:c>
+      <ns0:c r="E36" s="1" t="n">
+        <ns0:v>350.26</ns0:v>
+      </ns0:c>
       <ns0:c r="F36" s="1" t="n">
         <ns0:v>0</ns0:v>
       </ns0:c>
@@ -5922,7 +6130,9 @@
       <ns0:c r="P36" s="1" t="n">
         <ns0:v>65</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q36"/>
+      <ns0:c s="1" r="Q36" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="37" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A37" s="6" t="n">
@@ -5934,8 +6144,12 @@
       <ns0:c r="C37" s="1" t="n">
         <ns0:v>9</ns0:v>
       </ns0:c>
-      <ns0:c r="D37" s="1"/>
-      <ns0:c r="E37" s="1"/>
+      <ns0:c r="D37" s="1" t="n">
+        <ns0:v>415.25</ns0:v>
+      </ns0:c>
+      <ns0:c r="E37" s="1" t="n">
+        <ns0:v>276.08</ns0:v>
+      </ns0:c>
       <ns0:c r="F37" s="1" t="n">
         <ns0:v>0</ns0:v>
       </ns0:c>
@@ -5969,7 +6183,9 @@
       <ns0:c r="P37" s="1" t="n">
         <ns0:v>65</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q37"/>
+      <ns0:c s="1" r="Q37" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="38" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A38" s="6" t="n">
@@ -5981,8 +6197,12 @@
       <ns0:c r="C38" s="1" t="n">
         <ns0:v>10</ns0:v>
       </ns0:c>
-      <ns0:c r="D38" s="1"/>
-      <ns0:c r="E38" s="1"/>
+      <ns0:c r="D38" s="1" t="n">
+        <ns0:v>234.16</ns0:v>
+      </ns0:c>
+      <ns0:c r="E38" s="1" t="n">
+        <ns0:v>186.94</ns0:v>
+      </ns0:c>
       <ns0:c r="F38" s="1" t="n">
         <ns0:v>-84</ns0:v>
       </ns0:c>
@@ -6016,7 +6236,9 @@
       <ns0:c r="P38" s="1" t="n">
         <ns0:v>65</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q38"/>
+      <ns0:c s="1" r="Q38" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="39" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A39" s="6" t="n">
@@ -6028,8 +6250,12 @@
       <ns0:c r="C39" s="1" t="n">
         <ns0:v>10</ns0:v>
       </ns0:c>
-      <ns0:c r="D39" s="1"/>
-      <ns0:c r="E39" s="1"/>
+      <ns0:c r="D39" s="1" t="n">
+        <ns0:v>234.16</ns0:v>
+      </ns0:c>
+      <ns0:c r="E39" s="1" t="n">
+        <ns0:v>182.88</ns0:v>
+      </ns0:c>
       <ns0:c r="F39" s="1" t="n">
         <ns0:v>-220</ns0:v>
       </ns0:c>
@@ -6063,7 +6289,9 @@
       <ns0:c r="P39" s="1" t="n">
         <ns0:v>65</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q39"/>
+      <ns0:c s="1" r="Q39" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="40" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A40" s="6" t="n">
@@ -6075,8 +6303,12 @@
       <ns0:c r="C40" s="1" t="n">
         <ns0:v>10</ns0:v>
       </ns0:c>
-      <ns0:c r="D40" s="1"/>
-      <ns0:c r="E40" s="1"/>
+      <ns0:c r="D40" s="1" t="n">
+        <ns0:v>234.16</ns0:v>
+      </ns0:c>
+      <ns0:c r="E40" s="1" t="n">
+        <ns0:v>184.11</ns0:v>
+      </ns0:c>
       <ns0:c r="F40" s="1" t="n">
         <ns0:v>-416</ns0:v>
       </ns0:c>
@@ -6110,7 +6342,9 @@
       <ns0:c r="P40" s="1" t="n">
         <ns0:v>65</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q40"/>
+      <ns0:c s="1" r="Q40" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="41" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A41" s="6" t="n">
@@ -6122,8 +6356,12 @@
       <ns0:c r="C41" s="1" t="n">
         <ns0:v>10</ns0:v>
       </ns0:c>
-      <ns0:c r="D41" s="1"/>
-      <ns0:c r="E41" s="1"/>
+      <ns0:c r="D41" s="1" t="n">
+        <ns0:v>234.16</ns0:v>
+      </ns0:c>
+      <ns0:c r="E41" s="1" t="n">
+        <ns0:v>177.47</ns0:v>
+      </ns0:c>
       <ns0:c r="F41" s="1" t="n">
         <ns0:v>-492.5</ns0:v>
       </ns0:c>
@@ -6157,7 +6395,9 @@
       <ns0:c r="P41" s="1" t="n">
         <ns0:v>65</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q41"/>
+      <ns0:c s="1" r="Q41" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="42" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A42" s="6" t="n">
@@ -6169,8 +6409,12 @@
       <ns0:c r="C42" s="1" t="n">
         <ns0:v>11</ns0:v>
       </ns0:c>
-      <ns0:c r="D42" s="1"/>
-      <ns0:c r="E42" s="1"/>
+      <ns0:c r="D42" s="1" t="n">
+        <ns0:v>155.22</ns0:v>
+      </ns0:c>
+      <ns0:c r="E42" s="1" t="n">
+        <ns0:v>178.71</ns0:v>
+      </ns0:c>
       <ns0:c r="F42" s="1" t="n">
         <ns0:v>-885.5</ns0:v>
       </ns0:c>
@@ -6204,7 +6448,9 @@
       <ns0:c r="P42" s="1" t="n">
         <ns0:v>65</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q42"/>
+      <ns0:c s="1" r="Q42" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="43" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A43" s="6" t="n">
@@ -6216,8 +6462,12 @@
       <ns0:c r="C43" s="1" t="n">
         <ns0:v>11</ns0:v>
       </ns0:c>
-      <ns0:c r="D43" s="1"/>
-      <ns0:c r="E43" s="1"/>
+      <ns0:c r="D43" s="1" t="n">
+        <ns0:v>155.22</ns0:v>
+      </ns0:c>
+      <ns0:c r="E43" s="1" t="n">
+        <ns0:v>175.52</ns0:v>
+      </ns0:c>
       <ns0:c r="F43" s="1" t="n">
         <ns0:v>-1026</ns0:v>
       </ns0:c>
@@ -6251,7 +6501,9 @@
       <ns0:c r="P43" s="1" t="n">
         <ns0:v>65</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q43"/>
+      <ns0:c s="1" r="Q43" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="44" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A44" s="6" t="n">
@@ -6263,8 +6515,12 @@
       <ns0:c r="C44" s="1" t="n">
         <ns0:v>11</ns0:v>
       </ns0:c>
-      <ns0:c r="D44" s="1"/>
-      <ns0:c r="E44" s="1"/>
+      <ns0:c r="D44" s="1" t="n">
+        <ns0:v>155.22</ns0:v>
+      </ns0:c>
+      <ns0:c r="E44" s="1" t="n">
+        <ns0:v>172.96</ns0:v>
+      </ns0:c>
       <ns0:c r="F44" s="1" t="n">
         <ns0:v>-1126</ns0:v>
       </ns0:c>
@@ -6298,7 +6554,9 @@
       <ns0:c r="P44" s="1" t="n">
         <ns0:v>65</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q44"/>
+      <ns0:c s="1" r="Q44" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="45" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A45" s="6" t="n">
@@ -6310,8 +6568,12 @@
       <ns0:c r="C45" s="1" t="n">
         <ns0:v>11</ns0:v>
       </ns0:c>
-      <ns0:c r="D45" s="1"/>
-      <ns0:c r="E45" s="1"/>
+      <ns0:c r="D45" s="1" t="n">
+        <ns0:v>155.22</ns0:v>
+      </ns0:c>
+      <ns0:c r="E45" s="1" t="n">
+        <ns0:v>186.94</ns0:v>
+      </ns0:c>
       <ns0:c r="F45" s="1" t="n">
         <ns0:v>-1121</ns0:v>
       </ns0:c>
@@ -6345,7 +6607,9 @@
       <ns0:c r="P45" s="1" t="n">
         <ns0:v>65</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q45"/>
+      <ns0:c s="1" r="Q45" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="46" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A46" s="6" t="n">
@@ -6357,8 +6621,12 @@
       <ns0:c r="C46" s="1" t="n">
         <ns0:v>12</ns0:v>
       </ns0:c>
-      <ns0:c r="D46" s="1"/>
-      <ns0:c r="E46" s="1"/>
+      <ns0:c r="D46" s="1" t="n">
+        <ns0:v>234.16</ns0:v>
+      </ns0:c>
+      <ns0:c r="E46" s="1" t="n">
+        <ns0:v>210</ns0:v>
+      </ns0:c>
       <ns0:c r="F46" s="1" t="n">
         <ns0:v>-1046</ns0:v>
       </ns0:c>
@@ -6392,7 +6660,9 @@
       <ns0:c r="P46" s="1" t="n">
         <ns0:v>65</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q46"/>
+      <ns0:c s="1" r="Q46" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="47" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A47" s="6" t="n">
@@ -6404,8 +6674,12 @@
       <ns0:c r="C47" s="1" t="n">
         <ns0:v>12</ns0:v>
       </ns0:c>
-      <ns0:c r="D47" s="1"/>
-      <ns0:c r="E47" s="1"/>
+      <ns0:c r="D47" s="1" t="n">
+        <ns0:v>234.16</ns0:v>
+      </ns0:c>
+      <ns0:c r="E47" s="1" t="n">
+        <ns0:v>274.6</ns0:v>
+      </ns0:c>
       <ns0:c r="F47" s="1" t="n">
         <ns0:v>-1046</ns0:v>
       </ns0:c>
@@ -6439,7 +6713,9 @@
       <ns0:c r="P47" s="1" t="n">
         <ns0:v>65</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q47"/>
+      <ns0:c s="1" r="Q47" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="48" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A48" s="6" t="n">
@@ -6451,8 +6727,12 @@
       <ns0:c r="C48" s="1" t="n">
         <ns0:v>12</ns0:v>
       </ns0:c>
-      <ns0:c r="D48" s="1"/>
-      <ns0:c r="E48" s="1"/>
+      <ns0:c r="D48" s="1" t="n">
+        <ns0:v>234.16</ns0:v>
+      </ns0:c>
+      <ns0:c r="E48" s="1" t="n">
+        <ns0:v>210</ns0:v>
+      </ns0:c>
       <ns0:c r="F48" s="1" t="n">
         <ns0:v>-1046</ns0:v>
       </ns0:c>
@@ -6486,7 +6766,9 @@
       <ns0:c r="P48" s="1" t="n">
         <ns0:v>65</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q48"/>
+      <ns0:c s="1" r="Q48" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="49" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A49" s="6" t="n">
@@ -6498,8 +6780,12 @@
       <ns0:c r="C49" s="1" t="n">
         <ns0:v>12</ns0:v>
       </ns0:c>
-      <ns0:c r="D49" s="1"/>
-      <ns0:c r="E49" s="1"/>
+      <ns0:c r="D49" s="1" t="n">
+        <ns0:v>234.16</ns0:v>
+      </ns0:c>
+      <ns0:c r="E49" s="1" t="n">
+        <ns0:v>204.16</ns0:v>
+      </ns0:c>
       <ns0:c r="F49" s="1" t="n">
         <ns0:v>-1026</ns0:v>
       </ns0:c>
@@ -6533,7 +6819,9 @@
       <ns0:c r="P49" s="1" t="n">
         <ns0:v>65</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q49"/>
+      <ns0:c s="1" r="Q49" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="50" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A50" s="6" t="n">
@@ -6545,8 +6833,12 @@
       <ns0:c r="C50" s="1" t="n">
         <ns0:v>13</ns0:v>
       </ns0:c>
-      <ns0:c r="D50" s="1"/>
-      <ns0:c r="E50" s="1"/>
+      <ns0:c r="D50" s="1" t="n">
+        <ns0:v>149.52</ns0:v>
+      </ns0:c>
+      <ns0:c r="E50" s="1" t="n">
+        <ns0:v>200.77</ns0:v>
+      </ns0:c>
       <ns0:c r="F50" s="1" t="n">
         <ns0:v>-951</ns0:v>
       </ns0:c>
@@ -6580,7 +6872,9 @@
       <ns0:c r="P50" s="1" t="n">
         <ns0:v>65</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q50"/>
+      <ns0:c s="1" r="Q50" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="51" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A51" s="6" t="n">
@@ -6592,8 +6886,12 @@
       <ns0:c r="C51" s="1" t="n">
         <ns0:v>13</ns0:v>
       </ns0:c>
-      <ns0:c r="D51" s="1"/>
-      <ns0:c r="E51" s="1"/>
+      <ns0:c r="D51" s="1" t="n">
+        <ns0:v>149.52</ns0:v>
+      </ns0:c>
+      <ns0:c r="E51" s="1" t="n">
+        <ns0:v>186.94</ns0:v>
+      </ns0:c>
       <ns0:c r="F51" s="1" t="n">
         <ns0:v>-803</ns0:v>
       </ns0:c>
@@ -6627,7 +6925,9 @@
       <ns0:c r="P51" s="1" t="n">
         <ns0:v>65</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q51"/>
+      <ns0:c s="1" r="Q51" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="52" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A52" s="6" t="n">
@@ -6639,8 +6939,12 @@
       <ns0:c r="C52" s="1" t="n">
         <ns0:v>13</ns0:v>
       </ns0:c>
-      <ns0:c r="D52" s="1"/>
-      <ns0:c r="E52" s="1"/>
+      <ns0:c r="D52" s="1" t="n">
+        <ns0:v>149.52</ns0:v>
+      </ns0:c>
+      <ns0:c r="E52" s="1" t="n">
+        <ns0:v>206.47</ns0:v>
+      </ns0:c>
       <ns0:c r="F52" s="1" t="n">
         <ns0:v>-724</ns0:v>
       </ns0:c>
@@ -6674,7 +6978,9 @@
       <ns0:c r="P52" s="1" t="n">
         <ns0:v>65</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q52"/>
+      <ns0:c s="1" r="Q52" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="53" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A53" s="6" t="n">
@@ -6686,8 +6992,12 @@
       <ns0:c r="C53" s="1" t="n">
         <ns0:v>13</ns0:v>
       </ns0:c>
-      <ns0:c r="D53" s="1"/>
-      <ns0:c r="E53" s="1"/>
+      <ns0:c r="D53" s="1" t="n">
+        <ns0:v>149.52</ns0:v>
+      </ns0:c>
+      <ns0:c r="E53" s="1" t="n">
+        <ns0:v>200.57</ns0:v>
+      </ns0:c>
       <ns0:c r="F53" s="1" t="n">
         <ns0:v>-689</ns0:v>
       </ns0:c>
@@ -6721,7 +7031,9 @@
       <ns0:c r="P53" s="1" t="n">
         <ns0:v>65</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q53"/>
+      <ns0:c s="1" r="Q53" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="54" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A54" s="6" t="n">
@@ -6733,8 +7045,12 @@
       <ns0:c r="C54" s="1" t="n">
         <ns0:v>14</ns0:v>
       </ns0:c>
-      <ns0:c r="D54" s="1"/>
-      <ns0:c r="E54" s="1"/>
+      <ns0:c r="D54" s="1" t="n">
+        <ns0:v>155.22</ns0:v>
+      </ns0:c>
+      <ns0:c r="E54" s="1" t="n">
+        <ns0:v>207.16</ns0:v>
+      </ns0:c>
       <ns0:c r="F54" s="1" t="n">
         <ns0:v>-538</ns0:v>
       </ns0:c>
@@ -6768,7 +7084,9 @@
       <ns0:c r="P54" s="1" t="n">
         <ns0:v>65</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q54"/>
+      <ns0:c s="1" r="Q54" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="55" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A55" s="6" t="n">
@@ -6780,8 +7098,12 @@
       <ns0:c r="C55" s="1" t="n">
         <ns0:v>14</ns0:v>
       </ns0:c>
-      <ns0:c r="D55" s="1"/>
-      <ns0:c r="E55" s="1"/>
+      <ns0:c r="D55" s="1" t="n">
+        <ns0:v>155.22</ns0:v>
+      </ns0:c>
+      <ns0:c r="E55" s="1" t="n">
+        <ns0:v>244.52</ns0:v>
+      </ns0:c>
       <ns0:c r="F55" s="1" t="n">
         <ns0:v>-407.5</ns0:v>
       </ns0:c>
@@ -6815,7 +7137,9 @@
       <ns0:c r="P55" s="1" t="n">
         <ns0:v>65</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q55"/>
+      <ns0:c s="1" r="Q55" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="56" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A56" s="6" t="n">
@@ -6827,8 +7151,12 @@
       <ns0:c r="C56" s="1" t="n">
         <ns0:v>14</ns0:v>
       </ns0:c>
-      <ns0:c r="D56" s="1"/>
-      <ns0:c r="E56" s="1"/>
+      <ns0:c r="D56" s="1" t="n">
+        <ns0:v>155.22</ns0:v>
+      </ns0:c>
+      <ns0:c r="E56" s="1" t="n">
+        <ns0:v>279.92</ns0:v>
+      </ns0:c>
       <ns0:c r="F56" s="1" t="n">
         <ns0:v>-152.5</ns0:v>
       </ns0:c>
@@ -6862,7 +7190,9 @@
       <ns0:c r="P56" s="1" t="n">
         <ns0:v>65</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q56"/>
+      <ns0:c s="1" r="Q56" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="57" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A57" s="6" t="n">
@@ -6874,8 +7204,12 @@
       <ns0:c r="C57" s="1" t="n">
         <ns0:v>14</ns0:v>
       </ns0:c>
-      <ns0:c r="D57" s="1"/>
-      <ns0:c r="E57" s="1"/>
+      <ns0:c r="D57" s="1" t="n">
+        <ns0:v>155.22</ns0:v>
+      </ns0:c>
+      <ns0:c r="E57" s="1" t="n">
+        <ns0:v>234.16</ns0:v>
+      </ns0:c>
       <ns0:c r="F57" s="1" t="n">
         <ns0:v>-30</ns0:v>
       </ns0:c>
@@ -6909,7 +7243,9 @@
       <ns0:c r="P57" s="1" t="n">
         <ns0:v>65</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q57"/>
+      <ns0:c s="1" r="Q57" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="58" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A58" s="6" t="n">
@@ -6921,8 +7257,12 @@
       <ns0:c r="C58" s="1" t="n">
         <ns0:v>15</ns0:v>
       </ns0:c>
-      <ns0:c r="D58" s="1"/>
-      <ns0:c r="E58" s="1"/>
+      <ns0:c r="D58" s="1" t="n">
+        <ns0:v>369.51</ns0:v>
+      </ns0:c>
+      <ns0:c r="E58" s="1" t="n">
+        <ns0:v>279.07</ns0:v>
+      </ns0:c>
       <ns0:c r="F58" s="1" t="n">
         <ns0:v>0</ns0:v>
       </ns0:c>
@@ -6956,7 +7296,9 @@
       <ns0:c r="P58" s="1" t="n">
         <ns0:v>65</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q58"/>
+      <ns0:c s="1" r="Q58" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="59" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A59" s="6" t="n">
@@ -6968,8 +7310,12 @@
       <ns0:c r="C59" s="1" t="n">
         <ns0:v>15</ns0:v>
       </ns0:c>
-      <ns0:c r="D59" s="1"/>
-      <ns0:c r="E59" s="1"/>
+      <ns0:c r="D59" s="1" t="n">
+        <ns0:v>369.35</ns0:v>
+      </ns0:c>
+      <ns0:c r="E59" s="1" t="n">
+        <ns0:v>310.42</ns0:v>
+      </ns0:c>
       <ns0:c r="F59" s="1" t="n">
         <ns0:v>0</ns0:v>
       </ns0:c>
@@ -7003,7 +7349,9 @@
       <ns0:c r="P59" s="1" t="n">
         <ns0:v>65</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q59"/>
+      <ns0:c s="1" r="Q59" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="60" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A60" s="6" t="n">
@@ -7015,8 +7363,12 @@
       <ns0:c r="C60" s="1" t="n">
         <ns0:v>15</ns0:v>
       </ns0:c>
-      <ns0:c r="D60" s="1"/>
-      <ns0:c r="E60" s="1"/>
+      <ns0:c r="D60" s="1" t="n">
+        <ns0:v>369.35</ns0:v>
+      </ns0:c>
+      <ns0:c r="E60" s="1" t="n">
+        <ns0:v>350.29</ns0:v>
+      </ns0:c>
       <ns0:c r="F60" s="1" t="n">
         <ns0:v>0</ns0:v>
       </ns0:c>
@@ -7050,7 +7402,9 @@
       <ns0:c r="P60" s="1" t="n">
         <ns0:v>65</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q60"/>
+      <ns0:c s="1" r="Q60" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="61" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A61" s="6" t="n">
@@ -7062,8 +7416,12 @@
       <ns0:c r="C61" s="1" t="n">
         <ns0:v>15</ns0:v>
       </ns0:c>
-      <ns0:c r="D61" s="1"/>
-      <ns0:c r="E61" s="1"/>
+      <ns0:c r="D61" s="1" t="n">
+        <ns0:v>369.35</ns0:v>
+      </ns0:c>
+      <ns0:c r="E61" s="1" t="n">
+        <ns0:v>380.95</ns0:v>
+      </ns0:c>
       <ns0:c r="F61" s="1" t="n">
         <ns0:v>0</ns0:v>
       </ns0:c>
@@ -7097,7 +7455,9 @@
       <ns0:c r="P61" s="1" t="n">
         <ns0:v>65</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q61"/>
+      <ns0:c s="1" r="Q61" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="62" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A62" s="6" t="n">
@@ -7109,8 +7469,12 @@
       <ns0:c r="C62" s="1" t="n">
         <ns0:v>16</ns0:v>
       </ns0:c>
-      <ns0:c r="D62" s="1"/>
-      <ns0:c r="E62" s="1"/>
+      <ns0:c r="D62" s="1" t="n">
+        <ns0:v>400</ns0:v>
+      </ns0:c>
+      <ns0:c r="E62" s="1" t="n">
+        <ns0:v>402.8</ns0:v>
+      </ns0:c>
       <ns0:c r="F62" s="1" t="n">
         <ns0:v>0</ns0:v>
       </ns0:c>
@@ -7144,7 +7508,9 @@
       <ns0:c r="P62" s="1" t="n">
         <ns0:v>65</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q62"/>
+      <ns0:c s="1" r="Q62" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="63" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A63" s="6" t="n">
@@ -7156,8 +7522,12 @@
       <ns0:c r="C63" s="1" t="n">
         <ns0:v>16</ns0:v>
       </ns0:c>
-      <ns0:c r="D63" s="1"/>
-      <ns0:c r="E63" s="1"/>
+      <ns0:c r="D63" s="1" t="n">
+        <ns0:v>415.25</ns0:v>
+      </ns0:c>
+      <ns0:c r="E63" s="1" t="n">
+        <ns0:v>419.7</ns0:v>
+      </ns0:c>
       <ns0:c r="F63" s="1" t="n">
         <ns0:v>0</ns0:v>
       </ns0:c>
@@ -7191,7 +7561,9 @@
       <ns0:c r="P63" s="1" t="n">
         <ns0:v>65</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q63"/>
+      <ns0:c s="1" r="Q63" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="64" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A64" s="6" t="n">
@@ -7203,8 +7575,12 @@
       <ns0:c r="C64" s="1" t="n">
         <ns0:v>16</ns0:v>
       </ns0:c>
-      <ns0:c r="D64" s="1"/>
-      <ns0:c r="E64" s="1"/>
+      <ns0:c r="D64" s="1" t="n">
+        <ns0:v>400</ns0:v>
+      </ns0:c>
+      <ns0:c r="E64" s="1" t="n">
+        <ns0:v>449.48</ns0:v>
+      </ns0:c>
       <ns0:c r="F64" s="1" t="n">
         <ns0:v>0</ns0:v>
       </ns0:c>
@@ -7238,7 +7614,9 @@
       <ns0:c r="P64" s="1" t="n">
         <ns0:v>65</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q64"/>
+      <ns0:c s="1" r="Q64" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="65" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A65" s="6" t="n">
@@ -7250,8 +7628,12 @@
       <ns0:c r="C65" s="1" t="n">
         <ns0:v>16</ns0:v>
       </ns0:c>
-      <ns0:c r="D65" s="1"/>
-      <ns0:c r="E65" s="1"/>
+      <ns0:c r="D65" s="1" t="n">
+        <ns0:v>400</ns0:v>
+      </ns0:c>
+      <ns0:c r="E65" s="1" t="n">
+        <ns0:v>434.2</ns0:v>
+      </ns0:c>
       <ns0:c r="F65" s="1" t="n">
         <ns0:v>0</ns0:v>
       </ns0:c>
@@ -7285,7 +7667,9 @@
       <ns0:c r="P65" s="1" t="n">
         <ns0:v>65</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q65"/>
+      <ns0:c s="1" r="Q65" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="66" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A66" s="6" t="n">
@@ -7297,8 +7681,12 @@
       <ns0:c r="C66" s="1" t="n">
         <ns0:v>17</ns0:v>
       </ns0:c>
-      <ns0:c r="D66" s="1"/>
-      <ns0:c r="E66" s="1"/>
+      <ns0:c r="D66" s="1" t="n">
+        <ns0:v>390.94</ns0:v>
+      </ns0:c>
+      <ns0:c r="E66" s="1" t="n">
+        <ns0:v>453.39</ns0:v>
+      </ns0:c>
       <ns0:c r="F66" s="1" t="n">
         <ns0:v>120</ns0:v>
       </ns0:c>
@@ -7332,7 +7720,9 @@
       <ns0:c r="P66" s="1" t="n">
         <ns0:v>65</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q66"/>
+      <ns0:c s="1" r="Q66" t="n">
+        <ns0:v>0</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="67" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A67" s="6" t="n">
@@ -7344,8 +7734,12 @@
       <ns0:c r="C67" s="1" t="n">
         <ns0:v>17</ns0:v>
       </ns0:c>
-      <ns0:c r="D67" s="1"/>
-      <ns0:c r="E67" s="1"/>
+      <ns0:c r="D67" s="1" t="n">
+        <ns0:v>390.54</ns0:v>
+      </ns0:c>
+      <ns0:c r="E67" s="1" t="n">
+        <ns0:v>445.91</ns0:v>
+      </ns0:c>
       <ns0:c r="F67" s="1" t="n">
         <ns0:v>272.5</ns0:v>
       </ns0:c>
@@ -7379,7 +7773,9 @@
       <ns0:c r="P67" s="1" t="n">
         <ns0:v>65</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q67"/>
+      <ns0:c s="1" r="Q67" t="n">
+        <ns0:v>0</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="68" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A68" s="6" t="n">
@@ -7391,8 +7787,12 @@
       <ns0:c r="C68" s="1" t="n">
         <ns0:v>17</ns0:v>
       </ns0:c>
-      <ns0:c r="D68" s="1"/>
-      <ns0:c r="E68" s="1"/>
+      <ns0:c r="D68" s="1" t="n">
+        <ns0:v>390.54</ns0:v>
+      </ns0:c>
+      <ns0:c r="E68" s="1" t="n">
+        <ns0:v>460</ns0:v>
+      </ns0:c>
       <ns0:c r="F68" s="1" t="n">
         <ns0:v>607.5</ns0:v>
       </ns0:c>
@@ -7426,7 +7826,9 @@
       <ns0:c r="P68" s="1" t="n">
         <ns0:v>65</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q68"/>
+      <ns0:c s="1" r="Q68" t="n">
+        <ns0:v>0</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="69" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A69" s="6" t="n">
@@ -7438,8 +7840,12 @@
       <ns0:c r="C69" s="1" t="n">
         <ns0:v>17</ns0:v>
       </ns0:c>
-      <ns0:c r="D69" s="1"/>
-      <ns0:c r="E69" s="1"/>
+      <ns0:c r="D69" s="1" t="n">
+        <ns0:v>390.54</ns0:v>
+      </ns0:c>
+      <ns0:c r="E69" s="1" t="n">
+        <ns0:v>433.64</ns0:v>
+      </ns0:c>
       <ns0:c r="F69" s="1" t="n">
         <ns0:v>670</ns0:v>
       </ns0:c>
@@ -7473,7 +7879,9 @@
       <ns0:c r="P69" s="1" t="n">
         <ns0:v>65</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q69"/>
+      <ns0:c s="1" r="Q69" t="n">
+        <ns0:v>0</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="70" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A70" s="6" t="n">
@@ -7485,8 +7893,12 @@
       <ns0:c r="C70" s="1" t="n">
         <ns0:v>18</ns0:v>
       </ns0:c>
-      <ns0:c r="D70" s="1"/>
-      <ns0:c r="E70" s="1"/>
+      <ns0:c r="D70" s="1" t="n">
+        <ns0:v>435.04</ns0:v>
+      </ns0:c>
+      <ns0:c r="E70" s="1" t="n">
+        <ns0:v>413.82</ns0:v>
+      </ns0:c>
       <ns0:c r="F70" s="1" t="n">
         <ns0:v>755</ns0:v>
       </ns0:c>
@@ -7520,7 +7932,9 @@
       <ns0:c r="P70" s="1" t="n">
         <ns0:v>65</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q70"/>
+      <ns0:c s="1" r="Q70" t="n">
+        <ns0:v>0</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="71" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A71" s="6" t="n">
@@ -7532,8 +7946,12 @@
       <ns0:c r="C71" s="1" t="n">
         <ns0:v>18</ns0:v>
       </ns0:c>
-      <ns0:c r="D71" s="1"/>
-      <ns0:c r="E71" s="1"/>
+      <ns0:c r="D71" s="1" t="n">
+        <ns0:v>435.04</ns0:v>
+      </ns0:c>
+      <ns0:c r="E71" s="1" t="n">
+        <ns0:v>413.35</ns0:v>
+      </ns0:c>
       <ns0:c r="F71" s="1" t="n">
         <ns0:v>794</ns0:v>
       </ns0:c>
@@ -7567,7 +7985,9 @@
       <ns0:c r="P71" s="1" t="n">
         <ns0:v>65</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q71"/>
+      <ns0:c s="1" r="Q71" t="n">
+        <ns0:v>0</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="72" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A72" s="6" t="n">
@@ -7579,8 +7999,12 @@
       <ns0:c r="C72" s="1" t="n">
         <ns0:v>18</ns0:v>
       </ns0:c>
-      <ns0:c r="D72" s="1"/>
-      <ns0:c r="E72" s="1"/>
+      <ns0:c r="D72" s="1" t="n">
+        <ns0:v>435.04</ns0:v>
+      </ns0:c>
+      <ns0:c r="E72" s="1" t="n">
+        <ns0:v>411.01</ns0:v>
+      </ns0:c>
       <ns0:c r="F72" s="1" t="n">
         <ns0:v>833</ns0:v>
       </ns0:c>
@@ -7614,7 +8038,9 @@
       <ns0:c r="P72" s="1" t="n">
         <ns0:v>65</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q72"/>
+      <ns0:c s="1" r="Q72" t="n">
+        <ns0:v>0</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="73" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A73" s="6" t="n">
@@ -7626,8 +8052,12 @@
       <ns0:c r="C73" s="1" t="n">
         <ns0:v>18</ns0:v>
       </ns0:c>
-      <ns0:c r="D73" s="1"/>
-      <ns0:c r="E73" s="1"/>
+      <ns0:c r="D73" s="1" t="n">
+        <ns0:v>435.04</ns0:v>
+      </ns0:c>
+      <ns0:c r="E73" s="1" t="n">
+        <ns0:v>390.38</ns0:v>
+      </ns0:c>
       <ns0:c r="F73" s="1" t="n">
         <ns0:v>833</ns0:v>
       </ns0:c>
@@ -7661,7 +8091,9 @@
       <ns0:c r="P73" s="1" t="n">
         <ns0:v>65</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q73"/>
+      <ns0:c s="1" r="Q73" t="n">
+        <ns0:v>0</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="74" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A74" s="6" t="n">
@@ -7673,8 +8105,12 @@
       <ns0:c r="C74" s="1" t="n">
         <ns0:v>19</ns0:v>
       </ns0:c>
-      <ns0:c r="D74" s="1"/>
-      <ns0:c r="E74" s="1"/>
+      <ns0:c r="D74" s="1" t="n">
+        <ns0:v>369.51</ns0:v>
+      </ns0:c>
+      <ns0:c r="E74" s="1" t="n">
+        <ns0:v>385.45</ns0:v>
+      </ns0:c>
       <ns0:c r="F74" s="1" t="n">
         <ns0:v>833</ns0:v>
       </ns0:c>
@@ -7708,7 +8144,9 @@
       <ns0:c r="P74" s="1" t="n">
         <ns0:v>65</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q74"/>
+      <ns0:c s="1" r="Q74" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="75" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A75" s="6" t="n">
@@ -7720,8 +8158,12 @@
       <ns0:c r="C75" s="1" t="n">
         <ns0:v>19</ns0:v>
       </ns0:c>
-      <ns0:c r="D75" s="1"/>
-      <ns0:c r="E75" s="1"/>
+      <ns0:c r="D75" s="1" t="n">
+        <ns0:v>369.51</ns0:v>
+      </ns0:c>
+      <ns0:c r="E75" s="1" t="n">
+        <ns0:v>358.07</ns0:v>
+      </ns0:c>
       <ns0:c r="F75" s="1" t="n">
         <ns0:v>613</ns0:v>
       </ns0:c>
@@ -7755,7 +8197,9 @@
       <ns0:c r="P75" s="1" t="n">
         <ns0:v>65</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q75"/>
+      <ns0:c s="1" r="Q75" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="76" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A76" s="6" t="n">
@@ -7767,8 +8211,12 @@
       <ns0:c r="C76" s="1" t="n">
         <ns0:v>19</ns0:v>
       </ns0:c>
-      <ns0:c r="D76" s="1"/>
-      <ns0:c r="E76" s="1"/>
+      <ns0:c r="D76" s="1" t="n">
+        <ns0:v>369.51</ns0:v>
+      </ns0:c>
+      <ns0:c r="E76" s="1" t="n">
+        <ns0:v>355.73</ns0:v>
+      </ns0:c>
       <ns0:c r="F76" s="1" t="n">
         <ns0:v>453</ns0:v>
       </ns0:c>
@@ -7802,7 +8250,9 @@
       <ns0:c r="P76" s="1" t="n">
         <ns0:v>65</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q76"/>
+      <ns0:c s="1" r="Q76" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="77" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A77" s="6" t="n">
@@ -7814,8 +8264,12 @@
       <ns0:c r="C77" s="1" t="n">
         <ns0:v>19</ns0:v>
       </ns0:c>
-      <ns0:c r="D77" s="1"/>
-      <ns0:c r="E77" s="1"/>
+      <ns0:c r="D77" s="1" t="n">
+        <ns0:v>369.51</ns0:v>
+      </ns0:c>
+      <ns0:c r="E77" s="1" t="n">
+        <ns0:v>345</ns0:v>
+      </ns0:c>
       <ns0:c r="F77" s="1" t="n">
         <ns0:v>368</ns0:v>
       </ns0:c>
@@ -7849,7 +8303,9 @@
       <ns0:c r="P77" s="1" t="n">
         <ns0:v>65</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q77"/>
+      <ns0:c s="1" r="Q77" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="78" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A78" s="6" t="n">
@@ -7861,8 +8317,12 @@
       <ns0:c r="C78" s="1" t="n">
         <ns0:v>20</ns0:v>
       </ns0:c>
-      <ns0:c r="D78" s="1"/>
-      <ns0:c r="E78" s="1"/>
+      <ns0:c r="D78" s="1" t="n">
+        <ns0:v>195</ns0:v>
+      </ns0:c>
+      <ns0:c r="E78" s="1" t="n">
+        <ns0:v>330.79</ns0:v>
+      </ns0:c>
       <ns0:c r="F78" s="1" t="n">
         <ns0:v>288</ns0:v>
       </ns0:c>
@@ -7896,7 +8356,9 @@
       <ns0:c r="P78" s="1" t="n">
         <ns0:v>65</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q78"/>
+      <ns0:c s="1" r="Q78" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="79" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A79" s="6" t="n">
@@ -7908,8 +8370,12 @@
       <ns0:c r="C79" s="1" t="n">
         <ns0:v>20</ns0:v>
       </ns0:c>
-      <ns0:c r="D79" s="1"/>
-      <ns0:c r="E79" s="1"/>
+      <ns0:c r="D79" s="1" t="n">
+        <ns0:v>195</ns0:v>
+      </ns0:c>
+      <ns0:c r="E79" s="1" t="n">
+        <ns0:v>275.26</ns0:v>
+      </ns0:c>
       <ns0:c r="F79" s="1" t="n">
         <ns0:v>198</ns0:v>
       </ns0:c>
@@ -7943,7 +8409,9 @@
       <ns0:c r="P79" s="1" t="n">
         <ns0:v>65</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q79"/>
+      <ns0:c s="1" r="Q79" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="80" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A80" s="6" t="n">
@@ -7955,8 +8423,12 @@
       <ns0:c r="C80" s="1" t="n">
         <ns0:v>20</ns0:v>
       </ns0:c>
-      <ns0:c r="D80" s="1"/>
-      <ns0:c r="E80" s="1"/>
+      <ns0:c r="D80" s="1" t="n">
+        <ns0:v>195</ns0:v>
+      </ns0:c>
+      <ns0:c r="E80" s="1" t="n">
+        <ns0:v>282.13</ns0:v>
+      </ns0:c>
       <ns0:c r="F80" s="1" t="n">
         <ns0:v>65</ns0:v>
       </ns0:c>
@@ -7990,7 +8462,9 @@
       <ns0:c r="P80" s="1" t="n">
         <ns0:v>65</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q80"/>
+      <ns0:c s="1" r="Q80" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="81" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A81" s="6" t="n">
@@ -8002,8 +8476,12 @@
       <ns0:c r="C81" s="1" t="n">
         <ns0:v>20</ns0:v>
       </ns0:c>
-      <ns0:c r="D81" s="1"/>
-      <ns0:c r="E81" s="1"/>
+      <ns0:c r="D81" s="1" t="n">
+        <ns0:v>195</ns0:v>
+      </ns0:c>
+      <ns0:c r="E81" s="1" t="n">
+        <ns0:v>328.38</ns0:v>
+      </ns0:c>
       <ns0:c r="F81" s="1" t="n">
         <ns0:v>62</ns0:v>
       </ns0:c>
@@ -8037,7 +8515,9 @@
       <ns0:c r="P81" s="1" t="n">
         <ns0:v>65</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q81"/>
+      <ns0:c s="1" r="Q81" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="82" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A82" s="6" t="n">
@@ -8049,8 +8529,12 @@
       <ns0:c r="C82" s="1" t="n">
         <ns0:v>21</ns0:v>
       </ns0:c>
-      <ns0:c r="D82" s="1"/>
-      <ns0:c r="E82" s="1"/>
+      <ns0:c r="D82" s="1" t="n">
+        <ns0:v>167.11</ns0:v>
+      </ns0:c>
+      <ns0:c r="E82" s="1" t="n">
+        <ns0:v>328.38</ns0:v>
+      </ns0:c>
       <ns0:c r="F82" s="1" t="n">
         <ns0:v>48</ns0:v>
       </ns0:c>
@@ -8084,7 +8568,9 @@
       <ns0:c r="P82" s="1" t="n">
         <ns0:v>65</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q82"/>
+      <ns0:c s="1" r="Q82" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="83" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A83" s="6" t="n">
@@ -8096,8 +8582,12 @@
       <ns0:c r="C83" s="1" t="n">
         <ns0:v>21</ns0:v>
       </ns0:c>
-      <ns0:c r="D83" s="1"/>
-      <ns0:c r="E83" s="1"/>
+      <ns0:c r="D83" s="1" t="n">
+        <ns0:v>167.11</ns0:v>
+      </ns0:c>
+      <ns0:c r="E83" s="1" t="n">
+        <ns0:v>353.54</ns0:v>
+      </ns0:c>
       <ns0:c r="F83" s="1" t="n">
         <ns0:v>48</ns0:v>
       </ns0:c>
@@ -8131,7 +8621,9 @@
       <ns0:c r="P83" s="1" t="n">
         <ns0:v>65</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q83"/>
+      <ns0:c s="1" r="Q83" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="84" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A84" s="6" t="n">
@@ -8143,8 +8635,12 @@
       <ns0:c r="C84" s="1" t="n">
         <ns0:v>21</ns0:v>
       </ns0:c>
-      <ns0:c r="D84" s="1"/>
-      <ns0:c r="E84" s="1"/>
+      <ns0:c r="D84" s="1" t="n">
+        <ns0:v>167.11</ns0:v>
+      </ns0:c>
+      <ns0:c r="E84" s="1" t="n">
+        <ns0:v>354.69</ns0:v>
+      </ns0:c>
       <ns0:c r="F84" s="1" t="n">
         <ns0:v>32</ns0:v>
       </ns0:c>
@@ -8178,7 +8674,9 @@
       <ns0:c r="P84" s="1" t="n">
         <ns0:v>65</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q84"/>
+      <ns0:c s="1" r="Q84" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="85" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A85" s="6" t="n">
@@ -8190,8 +8688,12 @@
       <ns0:c r="C85" s="1" t="n">
         <ns0:v>21</ns0:v>
       </ns0:c>
-      <ns0:c r="D85" s="1"/>
-      <ns0:c r="E85" s="1"/>
+      <ns0:c r="D85" s="1" t="n">
+        <ns0:v>167.11</ns0:v>
+      </ns0:c>
+      <ns0:c r="E85" s="1" t="n">
+        <ns0:v>358.07</ns0:v>
+      </ns0:c>
       <ns0:c r="F85" s="1" t="n">
         <ns0:v>16</ns0:v>
       </ns0:c>
@@ -8225,7 +8727,9 @@
       <ns0:c r="P85" s="1" t="n">
         <ns0:v>65</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q85"/>
+      <ns0:c s="1" r="Q85" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="86" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A86" s="6" t="n">
@@ -8237,8 +8741,12 @@
       <ns0:c r="C86" s="1" t="n">
         <ns0:v>22</ns0:v>
       </ns0:c>
-      <ns0:c r="D86" s="1"/>
-      <ns0:c r="E86" s="1"/>
+      <ns0:c r="D86" s="1" t="n">
+        <ns0:v>270</ns0:v>
+      </ns0:c>
+      <ns0:c r="E86" s="1" t="n">
+        <ns0:v>390.54</ns0:v>
+      </ns0:c>
       <ns0:c r="F86" s="1" t="n">
         <ns0:v>0</ns0:v>
       </ns0:c>
@@ -8272,7 +8780,9 @@
       <ns0:c r="P86" s="1" t="n">
         <ns0:v>65</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q86"/>
+      <ns0:c s="1" r="Q86" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="87" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A87" s="6" t="n">
@@ -8284,8 +8794,12 @@
       <ns0:c r="C87" s="1" t="n">
         <ns0:v>22</ns0:v>
       </ns0:c>
-      <ns0:c r="D87" s="1"/>
-      <ns0:c r="E87" s="1"/>
+      <ns0:c r="D87" s="1" t="n">
+        <ns0:v>270</ns0:v>
+      </ns0:c>
+      <ns0:c r="E87" s="1" t="n">
+        <ns0:v>362.98</ns0:v>
+      </ns0:c>
       <ns0:c r="F87" s="1" t="n">
         <ns0:v>0</ns0:v>
       </ns0:c>
@@ -8319,7 +8833,9 @@
       <ns0:c r="P87" s="1" t="n">
         <ns0:v>65</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q87"/>
+      <ns0:c s="1" r="Q87" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="88" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A88" s="6" t="n">
@@ -8331,8 +8847,12 @@
       <ns0:c r="C88" s="1" t="n">
         <ns0:v>22</ns0:v>
       </ns0:c>
-      <ns0:c r="D88" s="1"/>
-      <ns0:c r="E88" s="1"/>
+      <ns0:c r="D88" s="1" t="n">
+        <ns0:v>270</ns0:v>
+      </ns0:c>
+      <ns0:c r="E88" s="1" t="n">
+        <ns0:v>353</ns0:v>
+      </ns0:c>
       <ns0:c r="F88" s="1" t="n">
         <ns0:v>0</ns0:v>
       </ns0:c>
@@ -8366,7 +8886,9 @@
       <ns0:c r="P88" s="1" t="n">
         <ns0:v>65</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q88"/>
+      <ns0:c s="1" r="Q88" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="89" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A89" s="6" t="n">
@@ -8378,8 +8900,12 @@
       <ns0:c r="C89" s="1" t="n">
         <ns0:v>22</ns0:v>
       </ns0:c>
-      <ns0:c r="D89" s="1"/>
-      <ns0:c r="E89" s="1"/>
+      <ns0:c r="D89" s="1" t="n">
+        <ns0:v>270</ns0:v>
+      </ns0:c>
+      <ns0:c r="E89" s="1" t="n">
+        <ns0:v>310</ns0:v>
+      </ns0:c>
       <ns0:c r="F89" s="1" t="n">
         <ns0:v>0</ns0:v>
       </ns0:c>
@@ -8413,7 +8939,9 @@
       <ns0:c r="P89" s="1" t="n">
         <ns0:v>65</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q89"/>
+      <ns0:c s="1" r="Q89" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="90" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A90" s="6" t="n">
@@ -8425,8 +8953,12 @@
       <ns0:c r="C90" s="1" t="n">
         <ns0:v>23</ns0:v>
       </ns0:c>
-      <ns0:c r="D90" s="1"/>
-      <ns0:c r="E90" s="1"/>
+      <ns0:c r="D90" s="1" t="n">
+        <ns0:v>234.16</ns0:v>
+      </ns0:c>
+      <ns0:c r="E90" s="1" t="n">
+        <ns0:v>279.92</ns0:v>
+      </ns0:c>
       <ns0:c r="F90" s="1" t="n">
         <ns0:v>35</ns0:v>
       </ns0:c>
@@ -8460,7 +8992,9 @@
       <ns0:c r="P90" s="1" t="n">
         <ns0:v>65</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q90"/>
+      <ns0:c s="1" r="Q90" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="91" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A91" s="6" t="n">
@@ -8472,8 +9006,12 @@
       <ns0:c r="C91" s="1" t="n">
         <ns0:v>23</ns0:v>
       </ns0:c>
-      <ns0:c r="D91" s="1"/>
-      <ns0:c r="E91" s="1"/>
+      <ns0:c r="D91" s="1" t="n">
+        <ns0:v>234.16</ns0:v>
+      </ns0:c>
+      <ns0:c r="E91" s="1" t="n">
+        <ns0:v>350.29</ns0:v>
+      </ns0:c>
       <ns0:c r="F91" s="1" t="n">
         <ns0:v>35</ns0:v>
       </ns0:c>
@@ -8507,7 +9045,9 @@
       <ns0:c r="P91" s="1" t="n">
         <ns0:v>65</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q91"/>
+      <ns0:c s="1" r="Q91" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="92" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A92" s="6" t="n">
@@ -8519,8 +9059,12 @@
       <ns0:c r="C92" s="1" t="n">
         <ns0:v>23</ns0:v>
       </ns0:c>
-      <ns0:c r="D92" s="1"/>
-      <ns0:c r="E92" s="1"/>
+      <ns0:c r="D92" s="1" t="n">
+        <ns0:v>234.16</ns0:v>
+      </ns0:c>
+      <ns0:c r="E92" s="1" t="n">
+        <ns0:v>335.98</ns0:v>
+      </ns0:c>
       <ns0:c r="F92" s="1" t="n">
         <ns0:v>35</ns0:v>
       </ns0:c>
@@ -8554,7 +9098,9 @@
       <ns0:c r="P92" s="1" t="n">
         <ns0:v>65</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q92"/>
+      <ns0:c s="1" r="Q92" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="93" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A93" s="6" t="n">
@@ -8566,8 +9112,12 @@
       <ns0:c r="C93" s="1" t="n">
         <ns0:v>23</ns0:v>
       </ns0:c>
-      <ns0:c r="D93" s="1"/>
-      <ns0:c r="E93" s="1"/>
+      <ns0:c r="D93" s="1" t="n">
+        <ns0:v>234.16</ns0:v>
+      </ns0:c>
+      <ns0:c r="E93" s="1" t="n">
+        <ns0:v>282.1</ns0:v>
+      </ns0:c>
       <ns0:c r="F93" s="1" t="n">
         <ns0:v>35</ns0:v>
       </ns0:c>
@@ -8601,7 +9151,9 @@
       <ns0:c r="P93" s="1" t="n">
         <ns0:v>65</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q93"/>
+      <ns0:c s="1" r="Q93" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="94" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A94" s="6" t="n">
@@ -8613,8 +9165,12 @@
       <ns0:c r="C94" s="1" t="n">
         <ns0:v>24</ns0:v>
       </ns0:c>
-      <ns0:c r="D94" s="1"/>
-      <ns0:c r="E94" s="1"/>
+      <ns0:c r="D94" s="1" t="n">
+        <ns0:v>155.86</ns0:v>
+      </ns0:c>
+      <ns0:c r="E94" s="1" t="n">
+        <ns0:v>310</ns0:v>
+      </ns0:c>
       <ns0:c r="F94" s="1" t="n">
         <ns0:v>35</ns0:v>
       </ns0:c>
@@ -8648,7 +9204,9 @@
       <ns0:c r="P94" s="1" t="n">
         <ns0:v>65</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q94"/>
+      <ns0:c s="1" r="Q94" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="95" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A95" s="6" t="n">
@@ -8660,8 +9218,12 @@
       <ns0:c r="C95" s="1" t="n">
         <ns0:v>24</ns0:v>
       </ns0:c>
-      <ns0:c r="D95" s="1"/>
-      <ns0:c r="E95" s="1"/>
+      <ns0:c r="D95" s="1" t="n">
+        <ns0:v>155.86</ns0:v>
+      </ns0:c>
+      <ns0:c r="E95" s="1" t="n">
+        <ns0:v>287.55</ns0:v>
+      </ns0:c>
       <ns0:c r="F95" s="1" t="n">
         <ns0:v>35</ns0:v>
       </ns0:c>
@@ -8695,7 +9257,9 @@
       <ns0:c r="P95" s="1" t="n">
         <ns0:v>65</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q95"/>
+      <ns0:c s="1" r="Q95" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="96" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A96" s="6" t="n">
@@ -8707,8 +9271,12 @@
       <ns0:c r="C96" s="1" t="n">
         <ns0:v>24</ns0:v>
       </ns0:c>
-      <ns0:c r="D96" s="1"/>
-      <ns0:c r="E96" s="1"/>
+      <ns0:c r="D96" s="1" t="n">
+        <ns0:v>155.86</ns0:v>
+      </ns0:c>
+      <ns0:c r="E96" s="1" t="n">
+        <ns0:v>276.08</ns0:v>
+      </ns0:c>
       <ns0:c r="F96" s="1" t="n">
         <ns0:v>35</ns0:v>
       </ns0:c>
@@ -8742,7 +9310,9 @@
       <ns0:c r="P96" s="1" t="n">
         <ns0:v>65</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q96"/>
+      <ns0:c s="1" r="Q96" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="97" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A97" s="6" t="n">
@@ -8756,8 +9326,12 @@
       <ns0:c r="C97" s="1" t="n">
         <ns0:v>24</ns0:v>
       </ns0:c>
-      <ns0:c r="D97" s="1"/>
-      <ns0:c r="E97" s="1"/>
+      <ns0:c r="D97" s="1" t="n">
+        <ns0:v>155.86</ns0:v>
+      </ns0:c>
+      <ns0:c r="E97" s="1" t="n">
+        <ns0:v>279.44</ns0:v>
+      </ns0:c>
       <ns0:c r="F97" s="1" t="n">
         <ns0:v>35</ns0:v>
       </ns0:c>
@@ -8791,7 +9365,9 @@
       <ns0:c r="P97" s="1" t="n">
         <ns0:v>65</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q97"/>
+      <ns0:c s="1" r="Q97" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
   </ns0:sheetData>
   <conditionalFormatting sqref="A1:B1">
